--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A2C695-01A2-4664-B1D5-FFB9F6371D91}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D7872D-B713-4D94-94FF-9877221D20D6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -657,23 +657,34 @@
       <c r="D6" s="1">
         <v>45</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1">
+        <f>33.4+35</f>
+        <v>68.400000000000006</v>
+      </c>
       <c r="F6" s="1">
         <v>35.1</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1">
+        <v>45.6</v>
+      </c>
       <c r="H6" s="1">
         <v>30</v>
       </c>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1">
+        <v>46.3</v>
+      </c>
       <c r="J6" s="1">
         <v>12</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="K6" s="1">
+        <v>7.9</v>
+      </c>
       <c r="L6" s="1">
         <v>13.5</v>
       </c>
-      <c r="M6" s="1"/>
+      <c r="M6" s="1">
+        <v>13.4</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1604,21 +1615,21 @@
       <c r="M35" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1662,13 +1673,13 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1693,9 +1704,9 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -1783,23 +1794,34 @@
       <c r="D43" s="1">
         <v>15</v>
       </c>
-      <c r="E43" s="1"/>
+      <c r="E43" s="1">
+        <f>19.9+15</f>
+        <v>34.9</v>
+      </c>
       <c r="F43" s="1">
         <v>10</v>
       </c>
-      <c r="G43" s="1"/>
+      <c r="G43" s="1">
+        <v>20.7</v>
+      </c>
       <c r="H43" s="1">
         <v>7.4</v>
       </c>
-      <c r="I43" s="1"/>
+      <c r="I43" s="1">
+        <v>19.8</v>
+      </c>
       <c r="J43" s="1">
         <v>5</v>
       </c>
-      <c r="K43" s="1"/>
+      <c r="K43" s="1">
+        <v>5.6</v>
+      </c>
       <c r="L43" s="1">
         <v>2.8</v>
       </c>
-      <c r="M43" s="1"/>
+      <c r="M43" s="1">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
@@ -2730,21 +2752,21 @@
       <c r="M72" s="1"/>
     </row>
     <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -2788,13 +2810,13 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -2819,9 +2841,9 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -2909,23 +2931,34 @@
       <c r="D79" s="1">
         <v>22</v>
       </c>
-      <c r="E79" s="1"/>
+      <c r="E79" s="1">
+        <f>23.6+20</f>
+        <v>43.6</v>
+      </c>
       <c r="F79" s="1">
         <v>6</v>
       </c>
-      <c r="G79" s="1"/>
+      <c r="G79" s="1">
+        <v>12.7</v>
+      </c>
       <c r="H79" s="1">
         <v>4.5</v>
       </c>
-      <c r="I79" s="1"/>
+      <c r="I79" s="1">
+        <v>21.2</v>
+      </c>
       <c r="J79" s="1">
         <v>5</v>
       </c>
-      <c r="K79" s="1"/>
+      <c r="K79" s="1">
+        <v>6.5</v>
+      </c>
       <c r="L79" s="1">
         <v>2.7</v>
       </c>
-      <c r="M79" s="1"/>
+      <c r="M79" s="1">
+        <v>9.1999999999999993</v>
+      </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
@@ -3857,6 +3890,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="A74:M74"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="B76:B77"/>
@@ -3866,24 +3917,6 @@
     <mergeCell ref="J76:K76"/>
     <mergeCell ref="L76:M76"/>
     <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D7872D-B713-4D94-94FF-9877221D20D6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA45D33-2688-4FFF-BB87-E22CA45208D6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="22">
   <si>
     <t>№ п/п</t>
   </si>
@@ -92,6 +92,12 @@
   <si>
     <t>День недели</t>
   </si>
+  <si>
+    <t>МАРИУПОЛЬ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
@@ -147,7 +153,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -170,23 +176,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,33 +497,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:O108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
     <col min="2" max="2" width="9.85546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" style="2" customWidth="1"/>
-    <col min="4" max="13" width="10.7109375" style="2" customWidth="1"/>
+    <col min="4" max="15" width="10.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -534,42 +565,52 @@
       <c r="M2" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="N2" s="1">
+        <v>14</v>
+      </c>
+      <c r="O2" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6" t="s">
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -600,8 +641,14 @@
       <c r="M4" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -642,8 +689,14 @@
       <c r="M5" s="1">
         <v>16.899999999999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="1">
+        <v>5</v>
+      </c>
+      <c r="O5" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -685,8 +738,14 @@
       <c r="M6" s="1">
         <v>13.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="1">
+        <v>5</v>
+      </c>
+      <c r="O6" s="1">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -700,25 +759,41 @@
       <c r="D7" s="1">
         <v>45</v>
       </c>
-      <c r="E7" s="1"/>
+      <c r="E7" s="1">
+        <v>41.9</v>
+      </c>
       <c r="F7" s="1">
         <v>35.1</v>
       </c>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1">
+        <v>36.6</v>
+      </c>
       <c r="H7" s="1">
         <v>30</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1">
+        <v>39.1</v>
+      </c>
       <c r="J7" s="1">
         <v>12</v>
       </c>
-      <c r="K7" s="1"/>
+      <c r="K7" s="1">
+        <v>12.2</v>
+      </c>
       <c r="L7" s="1">
         <v>13.5</v>
       </c>
-      <c r="M7" s="1"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M7" s="1">
+        <v>23.6</v>
+      </c>
+      <c r="N7" s="1">
+        <v>5</v>
+      </c>
+      <c r="O7" s="1">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -732,25 +807,41 @@
       <c r="D8" s="1">
         <v>45</v>
       </c>
-      <c r="E8" s="1"/>
+      <c r="E8" s="1">
+        <v>42.7</v>
+      </c>
       <c r="F8" s="1">
         <v>35.1</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1">
+        <v>36.700000000000003</v>
+      </c>
       <c r="H8" s="1">
         <v>30</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1">
+        <v>39.1</v>
+      </c>
       <c r="J8" s="1">
         <v>12</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1">
+        <v>12.3</v>
+      </c>
       <c r="L8" s="1">
         <v>13.5</v>
       </c>
-      <c r="M8" s="1"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M8" s="1">
+        <v>23.6</v>
+      </c>
+      <c r="N8" s="1">
+        <v>5</v>
+      </c>
+      <c r="O8" s="1">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -764,25 +855,41 @@
       <c r="D9" s="1">
         <v>45</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="1">
+        <v>77.599999999999994</v>
+      </c>
       <c r="F9" s="1">
         <v>35.1</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1">
+        <v>36.799999999999997</v>
+      </c>
       <c r="H9" s="1">
         <v>30</v>
       </c>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1">
+        <v>39.1</v>
+      </c>
       <c r="J9" s="1">
         <v>12</v>
       </c>
-      <c r="K9" s="1"/>
+      <c r="K9" s="1">
+        <v>12.3</v>
+      </c>
       <c r="L9" s="1">
         <v>13.5</v>
       </c>
-      <c r="M9" s="1"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M9" s="1">
+        <v>23.6</v>
+      </c>
+      <c r="N9" s="1">
+        <v>5</v>
+      </c>
+      <c r="O9" s="1">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>6</v>
       </c>
@@ -808,13 +915,19 @@
       <c r="J10" s="1">
         <v>12</v>
       </c>
-      <c r="K10" s="1"/>
+      <c r="K10" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="L10" s="1">
         <v>13.5</v>
       </c>
       <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10" s="1">
+        <v>5</v>
+      </c>
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -845,8 +958,12 @@
         <v>13.5</v>
       </c>
       <c r="M11" s="1"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11" s="1">
+        <v>5</v>
+      </c>
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>8</v>
       </c>
@@ -877,8 +994,12 @@
         <v>13.5</v>
       </c>
       <c r="M12" s="1"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N12" s="1">
+        <v>5</v>
+      </c>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -909,8 +1030,12 @@
         <v>13.5</v>
       </c>
       <c r="M13" s="1"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N13" s="1">
+        <v>5</v>
+      </c>
+      <c r="O13" s="1"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>10</v>
       </c>
@@ -941,8 +1066,12 @@
         <v>13.5</v>
       </c>
       <c r="M14" s="1"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N14" s="1">
+        <v>5</v>
+      </c>
+      <c r="O14" s="1"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -973,8 +1102,12 @@
         <v>13.5</v>
       </c>
       <c r="M15" s="1"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N15" s="1">
+        <v>5</v>
+      </c>
+      <c r="O15" s="1"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>12</v>
       </c>
@@ -1005,8 +1138,12 @@
         <v>13.5</v>
       </c>
       <c r="M16" s="1"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N16" s="1">
+        <v>5</v>
+      </c>
+      <c r="O16" s="1"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1037,8 +1174,12 @@
         <v>13.5</v>
       </c>
       <c r="M17" s="1"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N17" s="1">
+        <v>5</v>
+      </c>
+      <c r="O17" s="1"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>14</v>
       </c>
@@ -1069,8 +1210,12 @@
         <v>13.5</v>
       </c>
       <c r="M18" s="1"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N18" s="1">
+        <v>5</v>
+      </c>
+      <c r="O18" s="1"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1101,8 +1246,12 @@
         <v>13.5</v>
       </c>
       <c r="M19" s="1"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N19" s="1">
+        <v>5</v>
+      </c>
+      <c r="O19" s="1"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -1133,8 +1282,12 @@
         <v>13.5</v>
       </c>
       <c r="M20" s="1"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N20" s="1">
+        <v>5</v>
+      </c>
+      <c r="O20" s="1"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -1165,8 +1318,12 @@
         <v>13.5</v>
       </c>
       <c r="M21" s="1"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N21" s="1">
+        <v>5</v>
+      </c>
+      <c r="O21" s="1"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -1197,8 +1354,12 @@
         <v>13.5</v>
       </c>
       <c r="M22" s="1"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N22" s="1">
+        <v>5</v>
+      </c>
+      <c r="O22" s="1"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -1229,8 +1390,12 @@
         <v>13.5</v>
       </c>
       <c r="M23" s="1"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N23" s="1">
+        <v>5</v>
+      </c>
+      <c r="O23" s="1"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -1261,8 +1426,12 @@
         <v>13.5</v>
       </c>
       <c r="M24" s="1"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N24" s="1">
+        <v>5</v>
+      </c>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -1293,8 +1462,12 @@
         <v>13.5</v>
       </c>
       <c r="M25" s="1"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N25" s="1">
+        <v>5</v>
+      </c>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -1325,8 +1498,12 @@
         <v>13.5</v>
       </c>
       <c r="M26" s="1"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N26" s="1">
+        <v>5</v>
+      </c>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -1357,8 +1534,12 @@
         <v>13.5</v>
       </c>
       <c r="M27" s="1"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N27" s="1">
+        <v>5</v>
+      </c>
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -1389,8 +1570,12 @@
         <v>13.5</v>
       </c>
       <c r="M28" s="1"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N28" s="1">
+        <v>5</v>
+      </c>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -1421,8 +1606,12 @@
         <v>13.5</v>
       </c>
       <c r="M29" s="1"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N29" s="1">
+        <v>5</v>
+      </c>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -1453,8 +1642,12 @@
         <v>13.5</v>
       </c>
       <c r="M30" s="1"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N30" s="1">
+        <v>5</v>
+      </c>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -1485,8 +1678,12 @@
         <v>13.5</v>
       </c>
       <c r="M31" s="1"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N31" s="1">
+        <v>5</v>
+      </c>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -1517,8 +1714,12 @@
         <v>13.5</v>
       </c>
       <c r="M32" s="1"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N32" s="1">
+        <v>5</v>
+      </c>
+      <c r="O32" s="1"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -1549,8 +1750,12 @@
         <v>13.5</v>
       </c>
       <c r="M33" s="1"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N33" s="1">
+        <v>5</v>
+      </c>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -1581,8 +1786,12 @@
         <v>13.5</v>
       </c>
       <c r="M34" s="1"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N34" s="1">
+        <v>5</v>
+      </c>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -1613,25 +1822,31 @@
         <v>13.5</v>
       </c>
       <c r="M35" s="1"/>
-    </row>
-    <row r="38" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
+      <c r="N35" s="1">
+        <v>5</v>
+      </c>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>1</v>
       </c>
@@ -1671,42 +1886,52 @@
       <c r="M39" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="N39" s="1">
+        <v>14</v>
+      </c>
+      <c r="O39" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6" t="s">
+      <c r="E40" s="4"/>
+      <c r="F40" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6" t="s">
+      <c r="G40" s="4"/>
+      <c r="H40" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6" t="s">
+      <c r="I40" s="4"/>
+      <c r="J40" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M40" s="6"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O40" s="4"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -1737,8 +1962,14 @@
       <c r="M41" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>1</v>
       </c>
@@ -1779,8 +2010,14 @@
       <c r="M42" s="1">
         <v>4.9000000000000004</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N42" s="1">
+        <v>3</v>
+      </c>
+      <c r="O42" s="1">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>2</v>
       </c>
@@ -1822,8 +2059,14 @@
       <c r="M43" s="1">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N43" s="1">
+        <v>3</v>
+      </c>
+      <c r="O43" s="1">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>3</v>
       </c>
@@ -1837,25 +2080,42 @@
       <c r="D44" s="1">
         <v>15</v>
       </c>
-      <c r="E44" s="1"/>
+      <c r="E44" s="1">
+        <f>29.6</f>
+        <v>29.6</v>
+      </c>
       <c r="F44" s="1">
         <v>10</v>
       </c>
-      <c r="G44" s="1"/>
+      <c r="G44" s="1">
+        <v>16.5</v>
+      </c>
       <c r="H44" s="1">
         <v>7.4</v>
       </c>
-      <c r="I44" s="1"/>
+      <c r="I44" s="1">
+        <v>17.899999999999999</v>
+      </c>
       <c r="J44" s="1">
         <v>5</v>
       </c>
-      <c r="K44" s="1"/>
+      <c r="K44" s="1">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="L44" s="1">
         <v>2.8</v>
       </c>
-      <c r="M44" s="1"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M44" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="N44" s="1">
+        <v>3</v>
+      </c>
+      <c r="O44" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>4</v>
       </c>
@@ -1869,25 +2129,41 @@
       <c r="D45" s="1">
         <v>15</v>
       </c>
-      <c r="E45" s="1"/>
+      <c r="E45" s="1">
+        <v>29.7</v>
+      </c>
       <c r="F45" s="1">
         <v>10</v>
       </c>
-      <c r="G45" s="1"/>
+      <c r="G45" s="1">
+        <v>16.5</v>
+      </c>
       <c r="H45" s="1">
         <v>7.4</v>
       </c>
-      <c r="I45" s="1"/>
+      <c r="I45" s="1">
+        <v>17.899999999999999</v>
+      </c>
       <c r="J45" s="1">
         <v>5</v>
       </c>
-      <c r="K45" s="1"/>
+      <c r="K45" s="1">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="L45" s="1">
         <v>2.8</v>
       </c>
-      <c r="M45" s="1"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M45" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="N45" s="1">
+        <v>3</v>
+      </c>
+      <c r="O45" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -1901,25 +2177,42 @@
       <c r="D46" s="1">
         <v>15</v>
       </c>
-      <c r="E46" s="1"/>
+      <c r="E46" s="1">
+        <f>29.7+15</f>
+        <v>44.7</v>
+      </c>
       <c r="F46" s="1">
         <v>10</v>
       </c>
-      <c r="G46" s="1"/>
+      <c r="G46" s="1">
+        <v>16.5</v>
+      </c>
       <c r="H46" s="1">
         <v>7.4</v>
       </c>
-      <c r="I46" s="1"/>
+      <c r="I46" s="1">
+        <v>17.899999999999999</v>
+      </c>
       <c r="J46" s="1">
         <v>5</v>
       </c>
-      <c r="K46" s="1"/>
+      <c r="K46" s="1">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="L46" s="1">
         <v>2.8</v>
       </c>
-      <c r="M46" s="1"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M46" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="N46" s="1">
+        <v>3</v>
+      </c>
+      <c r="O46" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>6</v>
       </c>
@@ -1950,8 +2243,12 @@
         <v>2.8</v>
       </c>
       <c r="M47" s="1"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N47" s="1">
+        <v>3</v>
+      </c>
+      <c r="O47" s="1"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>7</v>
       </c>
@@ -1982,8 +2279,12 @@
         <v>2.8</v>
       </c>
       <c r="M48" s="1"/>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N48" s="1">
+        <v>3</v>
+      </c>
+      <c r="O48" s="1"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>8</v>
       </c>
@@ -2014,8 +2315,12 @@
         <v>2.8</v>
       </c>
       <c r="M49" s="1"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N49" s="1">
+        <v>3</v>
+      </c>
+      <c r="O49" s="1"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>9</v>
       </c>
@@ -2046,8 +2351,12 @@
         <v>2.8</v>
       </c>
       <c r="M50" s="1"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N50" s="1">
+        <v>3</v>
+      </c>
+      <c r="O50" s="1"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>10</v>
       </c>
@@ -2078,8 +2387,12 @@
         <v>2.8</v>
       </c>
       <c r="M51" s="1"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N51" s="1">
+        <v>3</v>
+      </c>
+      <c r="O51" s="1"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>11</v>
       </c>
@@ -2110,8 +2423,12 @@
         <v>2.8</v>
       </c>
       <c r="M52" s="1"/>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N52" s="1">
+        <v>3</v>
+      </c>
+      <c r="O52" s="1"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>12</v>
       </c>
@@ -2142,8 +2459,12 @@
         <v>2.8</v>
       </c>
       <c r="M53" s="1"/>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N53" s="1">
+        <v>3</v>
+      </c>
+      <c r="O53" s="1"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>13</v>
       </c>
@@ -2174,8 +2495,12 @@
         <v>2.8</v>
       </c>
       <c r="M54" s="1"/>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N54" s="1">
+        <v>3</v>
+      </c>
+      <c r="O54" s="1"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>14</v>
       </c>
@@ -2206,8 +2531,12 @@
         <v>2.8</v>
       </c>
       <c r="M55" s="1"/>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N55" s="1">
+        <v>3</v>
+      </c>
+      <c r="O55" s="1"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>15</v>
       </c>
@@ -2238,8 +2567,12 @@
         <v>2.8</v>
       </c>
       <c r="M56" s="1"/>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N56" s="1">
+        <v>3</v>
+      </c>
+      <c r="O56" s="1"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>16</v>
       </c>
@@ -2270,8 +2603,12 @@
         <v>2.8</v>
       </c>
       <c r="M57" s="1"/>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N57" s="1">
+        <v>3</v>
+      </c>
+      <c r="O57" s="1"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>17</v>
       </c>
@@ -2302,8 +2639,12 @@
         <v>2.8</v>
       </c>
       <c r="M58" s="1"/>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N58" s="1">
+        <v>3</v>
+      </c>
+      <c r="O58" s="1"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>18</v>
       </c>
@@ -2334,8 +2675,12 @@
         <v>2.8</v>
       </c>
       <c r="M59" s="1"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N59" s="1">
+        <v>3</v>
+      </c>
+      <c r="O59" s="1"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>19</v>
       </c>
@@ -2366,8 +2711,12 @@
         <v>2.8</v>
       </c>
       <c r="M60" s="1"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N60" s="1">
+        <v>3</v>
+      </c>
+      <c r="O60" s="1"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>20</v>
       </c>
@@ -2398,8 +2747,12 @@
         <v>2.8</v>
       </c>
       <c r="M61" s="1"/>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N61" s="1">
+        <v>3</v>
+      </c>
+      <c r="O61" s="1"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>21</v>
       </c>
@@ -2430,8 +2783,12 @@
         <v>2.8</v>
       </c>
       <c r="M62" s="1"/>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N62" s="1">
+        <v>3</v>
+      </c>
+      <c r="O62" s="1"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>22</v>
       </c>
@@ -2462,8 +2819,12 @@
         <v>2.8</v>
       </c>
       <c r="M63" s="1"/>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N63" s="1">
+        <v>3</v>
+      </c>
+      <c r="O63" s="1"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>23</v>
       </c>
@@ -2494,8 +2855,12 @@
         <v>2.8</v>
       </c>
       <c r="M64" s="1"/>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N64" s="1">
+        <v>3</v>
+      </c>
+      <c r="O64" s="1"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>24</v>
       </c>
@@ -2526,8 +2891,12 @@
         <v>2.8</v>
       </c>
       <c r="M65" s="1"/>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N65" s="1">
+        <v>3</v>
+      </c>
+      <c r="O65" s="1"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>25</v>
       </c>
@@ -2558,8 +2927,12 @@
         <v>2.8</v>
       </c>
       <c r="M66" s="1"/>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N66" s="1">
+        <v>3</v>
+      </c>
+      <c r="O66" s="1"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>26</v>
       </c>
@@ -2590,8 +2963,12 @@
         <v>2.8</v>
       </c>
       <c r="M67" s="1"/>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N67" s="1">
+        <v>3</v>
+      </c>
+      <c r="O67" s="1"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>27</v>
       </c>
@@ -2622,8 +2999,12 @@
         <v>2.8</v>
       </c>
       <c r="M68" s="1"/>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N68" s="1">
+        <v>3</v>
+      </c>
+      <c r="O68" s="1"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>28</v>
       </c>
@@ -2654,8 +3035,12 @@
         <v>2.8</v>
       </c>
       <c r="M69" s="1"/>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N69" s="1">
+        <v>3</v>
+      </c>
+      <c r="O69" s="1"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>29</v>
       </c>
@@ -2686,8 +3071,12 @@
         <v>2.8</v>
       </c>
       <c r="M70" s="1"/>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N70" s="1">
+        <v>3</v>
+      </c>
+      <c r="O70" s="1"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>30</v>
       </c>
@@ -2718,8 +3107,12 @@
         <v>2.8</v>
       </c>
       <c r="M71" s="1"/>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N71" s="1">
+        <v>3</v>
+      </c>
+      <c r="O71" s="1"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>31</v>
       </c>
@@ -2750,25 +3143,31 @@
         <v>2.8</v>
       </c>
       <c r="M72" s="1"/>
-    </row>
-    <row r="74" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="4" t="s">
+      <c r="N72" s="1">
+        <v>3</v>
+      </c>
+      <c r="O72" s="1"/>
+    </row>
+    <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>1</v>
       </c>
@@ -2808,42 +3207,52 @@
       <c r="M75" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="N75" s="1">
+        <v>14</v>
+      </c>
+      <c r="O75" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6" t="s">
+      <c r="E76" s="4"/>
+      <c r="F76" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6" t="s">
+      <c r="G76" s="4"/>
+      <c r="H76" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K76" s="6"/>
-      <c r="L76" s="6" t="s">
+      <c r="I76" s="4"/>
+      <c r="J76" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M76" s="6"/>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O76" s="4"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -2874,8 +3283,14 @@
       <c r="M77" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N77" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>1</v>
       </c>
@@ -2916,8 +3331,14 @@
       <c r="M78" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N78" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O78" s="1">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>2</v>
       </c>
@@ -2959,8 +3380,14 @@
       <c r="M79" s="1">
         <v>9.1999999999999993</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N79" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O79" s="1">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>3</v>
       </c>
@@ -2974,25 +3401,41 @@
       <c r="D80" s="1">
         <v>22</v>
       </c>
-      <c r="E80" s="1"/>
+      <c r="E80" s="1">
+        <v>21</v>
+      </c>
       <c r="F80" s="1">
         <v>6</v>
       </c>
-      <c r="G80" s="1"/>
+      <c r="G80" s="1">
+        <v>11</v>
+      </c>
       <c r="H80" s="1">
         <v>4.5</v>
       </c>
-      <c r="I80" s="1"/>
+      <c r="I80" s="1">
+        <v>19</v>
+      </c>
       <c r="J80" s="1">
         <v>5</v>
       </c>
-      <c r="K80" s="1"/>
+      <c r="K80" s="1">
+        <v>7.8</v>
+      </c>
       <c r="L80" s="1">
         <v>2.7</v>
       </c>
-      <c r="M80" s="1"/>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M80" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="N80" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O80" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>4</v>
       </c>
@@ -3006,25 +3449,41 @@
       <c r="D81" s="1">
         <v>22</v>
       </c>
-      <c r="E81" s="1"/>
+      <c r="E81" s="1">
+        <v>21.3</v>
+      </c>
       <c r="F81" s="1">
         <v>6</v>
       </c>
-      <c r="G81" s="1"/>
+      <c r="G81" s="1">
+        <v>11</v>
+      </c>
       <c r="H81" s="1">
         <v>4.5</v>
       </c>
-      <c r="I81" s="1"/>
+      <c r="I81" s="1">
+        <v>19</v>
+      </c>
       <c r="J81" s="1">
         <v>5</v>
       </c>
-      <c r="K81" s="1"/>
+      <c r="K81" s="1">
+        <v>7.8</v>
+      </c>
       <c r="L81" s="1">
         <v>2.7</v>
       </c>
-      <c r="M81" s="1"/>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M81" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="N81" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O81" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>5</v>
       </c>
@@ -3038,25 +3497,42 @@
       <c r="D82" s="1">
         <v>22</v>
       </c>
-      <c r="E82" s="1"/>
+      <c r="E82" s="1">
+        <f>41.6</f>
+        <v>41.6</v>
+      </c>
       <c r="F82" s="1">
         <v>6</v>
       </c>
-      <c r="G82" s="1"/>
+      <c r="G82" s="1">
+        <v>11</v>
+      </c>
       <c r="H82" s="1">
         <v>4.5</v>
       </c>
-      <c r="I82" s="1"/>
+      <c r="I82" s="1">
+        <v>19</v>
+      </c>
       <c r="J82" s="1">
         <v>5</v>
       </c>
-      <c r="K82" s="1"/>
+      <c r="K82" s="1">
+        <v>7.8</v>
+      </c>
       <c r="L82" s="1">
         <v>2.7</v>
       </c>
-      <c r="M82" s="1"/>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M82" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="N82" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O82" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>6</v>
       </c>
@@ -3087,8 +3563,12 @@
         <v>2.7</v>
       </c>
       <c r="M83" s="1"/>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N83" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O83" s="1"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>7</v>
       </c>
@@ -3119,8 +3599,12 @@
         <v>2.7</v>
       </c>
       <c r="M84" s="1"/>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N84" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O84" s="1"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>8</v>
       </c>
@@ -3151,8 +3635,12 @@
         <v>2.7</v>
       </c>
       <c r="M85" s="1"/>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N85" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O85" s="1"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>9</v>
       </c>
@@ -3183,8 +3671,12 @@
         <v>2.7</v>
       </c>
       <c r="M86" s="1"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N86" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O86" s="1"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>10</v>
       </c>
@@ -3215,8 +3707,12 @@
         <v>2.7</v>
       </c>
       <c r="M87" s="1"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N87" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O87" s="1"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>11</v>
       </c>
@@ -3247,8 +3743,12 @@
         <v>2.7</v>
       </c>
       <c r="M88" s="1"/>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N88" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O88" s="1"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>12</v>
       </c>
@@ -3279,8 +3779,12 @@
         <v>2.7</v>
       </c>
       <c r="M89" s="1"/>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N89" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O89" s="1"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>13</v>
       </c>
@@ -3311,8 +3815,12 @@
         <v>2.7</v>
       </c>
       <c r="M90" s="1"/>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N90" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O90" s="1"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>14</v>
       </c>
@@ -3343,8 +3851,12 @@
         <v>2.7</v>
       </c>
       <c r="M91" s="1"/>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N91" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O91" s="1"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>15</v>
       </c>
@@ -3375,8 +3887,12 @@
         <v>2.7</v>
       </c>
       <c r="M92" s="1"/>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N92" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O92" s="1"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>16</v>
       </c>
@@ -3407,8 +3923,12 @@
         <v>2.7</v>
       </c>
       <c r="M93" s="1"/>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N93" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O93" s="1"/>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>17</v>
       </c>
@@ -3439,8 +3959,12 @@
         <v>2.7</v>
       </c>
       <c r="M94" s="1"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N94" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O94" s="1"/>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>18</v>
       </c>
@@ -3471,8 +3995,12 @@
         <v>2.7</v>
       </c>
       <c r="M95" s="1"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N95" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O95" s="1"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>19</v>
       </c>
@@ -3503,8 +4031,12 @@
         <v>2.7</v>
       </c>
       <c r="M96" s="1"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N96" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O96" s="1"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>20</v>
       </c>
@@ -3535,8 +4067,12 @@
         <v>2.7</v>
       </c>
       <c r="M97" s="1"/>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N97" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O97" s="1"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>21</v>
       </c>
@@ -3567,8 +4103,12 @@
         <v>2.7</v>
       </c>
       <c r="M98" s="1"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N98" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O98" s="1"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>22</v>
       </c>
@@ -3599,8 +4139,12 @@
         <v>2.7</v>
       </c>
       <c r="M99" s="1"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N99" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O99" s="1"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>23</v>
       </c>
@@ -3631,8 +4175,12 @@
         <v>2.7</v>
       </c>
       <c r="M100" s="1"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N100" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O100" s="1"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>24</v>
       </c>
@@ -3663,8 +4211,12 @@
         <v>2.7</v>
       </c>
       <c r="M101" s="1"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N101" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O101" s="1"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>25</v>
       </c>
@@ -3695,8 +4247,12 @@
         <v>2.7</v>
       </c>
       <c r="M102" s="1"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N102" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O102" s="1"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>26</v>
       </c>
@@ -3727,8 +4283,12 @@
         <v>2.7</v>
       </c>
       <c r="M103" s="1"/>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N103" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O103" s="1"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>27</v>
       </c>
@@ -3759,8 +4319,12 @@
         <v>2.7</v>
       </c>
       <c r="M104" s="1"/>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N104" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O104" s="1"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>28</v>
       </c>
@@ -3791,8 +4355,12 @@
         <v>2.7</v>
       </c>
       <c r="M105" s="1"/>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N105" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O105" s="1"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>29</v>
       </c>
@@ -3823,8 +4391,12 @@
         <v>2.7</v>
       </c>
       <c r="M106" s="1"/>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N106" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O106" s="1"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>30</v>
       </c>
@@ -3855,8 +4427,12 @@
         <v>2.7</v>
       </c>
       <c r="M107" s="1"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N107" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O107" s="1"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>31</v>
       </c>
@@ -3887,28 +4463,33 @@
         <v>2.7</v>
       </c>
       <c r="M108" s="1"/>
+      <c r="N108" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="O108" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
+  <mergeCells count="30">
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="H40:I40"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="N76:O76"/>
+    <mergeCell ref="A74:O74"/>
+    <mergeCell ref="A38:O38"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="B76:B77"/>
     <mergeCell ref="D76:E76"/>
@@ -3917,6 +4498,8 @@
     <mergeCell ref="J76:K76"/>
     <mergeCell ref="L76:M76"/>
     <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA45D33-2688-4FFF-BB87-E22CA45208D6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A96295-01CA-44DA-98E2-E8EDFA502720}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="21">
   <si>
     <t>№ п/п</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>МАРИУПОЛЬ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -208,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -573,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -608,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -903,29 +900,39 @@
       <c r="D10" s="1">
         <v>45</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="1">
+        <v>46.3</v>
+      </c>
       <c r="F10" s="1">
         <v>35.1</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1">
+        <v>35.799999999999997</v>
+      </c>
       <c r="H10" s="1">
         <v>30</v>
       </c>
-      <c r="I10" s="1"/>
+      <c r="I10" s="1">
+        <v>46.6</v>
+      </c>
       <c r="J10" s="1">
         <v>12</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>21</v>
+      <c r="K10" s="1">
+        <v>9.4</v>
       </c>
       <c r="L10" s="1">
         <v>13.5</v>
       </c>
-      <c r="M10" s="1"/>
+      <c r="M10" s="1">
+        <v>21</v>
+      </c>
       <c r="N10" s="1">
         <v>5</v>
       </c>
-      <c r="O10" s="1"/>
+      <c r="O10" s="1">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1828,23 +1835,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1894,13 +1901,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -1929,9 +1936,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2226,27 +2233,39 @@
       <c r="D47" s="1">
         <v>15</v>
       </c>
-      <c r="E47" s="1"/>
+      <c r="E47" s="1">
+        <v>36.9</v>
+      </c>
       <c r="F47" s="1">
         <v>10</v>
       </c>
-      <c r="G47" s="1"/>
+      <c r="G47" s="1">
+        <v>14</v>
+      </c>
       <c r="H47" s="1">
         <v>7.4</v>
       </c>
-      <c r="I47" s="1"/>
+      <c r="I47" s="1">
+        <v>14.8</v>
+      </c>
       <c r="J47" s="1">
         <v>5</v>
       </c>
-      <c r="K47" s="1"/>
+      <c r="K47" s="1">
+        <v>4.2</v>
+      </c>
       <c r="L47" s="1">
         <v>2.8</v>
       </c>
-      <c r="M47" s="1"/>
+      <c r="M47" s="1">
+        <v>3.4</v>
+      </c>
       <c r="N47" s="1">
         <v>3</v>
       </c>
-      <c r="O47" s="1"/>
+      <c r="O47" s="1">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
@@ -3149,23 +3168,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
-      <c r="N74" s="6"/>
-      <c r="O74" s="6"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3215,13 +3234,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3250,9 +3269,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3546,27 +3565,40 @@
       <c r="D83" s="1">
         <v>22</v>
       </c>
-      <c r="E83" s="1"/>
+      <c r="E83" s="1">
+        <f>31.3+3</f>
+        <v>34.299999999999997</v>
+      </c>
       <c r="F83" s="1">
         <v>6</v>
       </c>
-      <c r="G83" s="1"/>
+      <c r="G83" s="1">
+        <v>10.6</v>
+      </c>
       <c r="H83" s="1">
         <v>4.5</v>
       </c>
-      <c r="I83" s="1"/>
+      <c r="I83" s="1">
+        <v>16.899999999999999</v>
+      </c>
       <c r="J83" s="1">
         <v>5</v>
       </c>
-      <c r="K83" s="1"/>
+      <c r="K83" s="1">
+        <v>7.2</v>
+      </c>
       <c r="L83" s="1">
         <v>2.7</v>
       </c>
-      <c r="M83" s="1"/>
+      <c r="M83" s="1">
+        <v>7.9</v>
+      </c>
       <c r="N83" s="1">
         <v>2.5</v>
       </c>
-      <c r="O83" s="1"/>
+      <c r="O83" s="1">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
@@ -4470,20 +4502,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -4500,6 +4518,20 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A96295-01CA-44DA-98E2-E8EDFA502720}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A6E467-E67C-4A80-B411-6F5C7E6E8EF4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -948,27 +948,39 @@
       <c r="D11" s="1">
         <v>45</v>
       </c>
-      <c r="E11" s="1"/>
+      <c r="E11" s="1">
+        <v>39.299999999999997</v>
+      </c>
       <c r="F11" s="1">
         <v>35.1</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1">
+        <v>40.9</v>
+      </c>
       <c r="H11" s="1">
         <v>30</v>
       </c>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1">
+        <v>38.299999999999997</v>
+      </c>
       <c r="J11" s="1">
         <v>12</v>
       </c>
-      <c r="K11" s="1"/>
+      <c r="K11" s="1">
+        <v>7.5</v>
+      </c>
       <c r="L11" s="1">
         <v>13.5</v>
       </c>
-      <c r="M11" s="1"/>
+      <c r="M11" s="1">
+        <v>14.6</v>
+      </c>
       <c r="N11" s="1">
         <v>5</v>
       </c>
-      <c r="O11" s="1"/>
+      <c r="O11" s="1">
+        <v>7</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -1835,23 +1847,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1901,13 +1913,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -1936,9 +1948,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2281,27 +2293,40 @@
       <c r="D48" s="1">
         <v>15</v>
       </c>
-      <c r="E48" s="1"/>
+      <c r="E48" s="1">
+        <f>28.4</f>
+        <v>28.4</v>
+      </c>
       <c r="F48" s="1">
         <v>10</v>
       </c>
-      <c r="G48" s="1"/>
+      <c r="G48" s="1">
+        <v>11.9</v>
+      </c>
       <c r="H48" s="1">
         <v>7.4</v>
       </c>
-      <c r="I48" s="1"/>
+      <c r="I48" s="1">
+        <v>12.4</v>
+      </c>
       <c r="J48" s="1">
         <v>5</v>
       </c>
-      <c r="K48" s="1"/>
+      <c r="K48" s="1">
+        <v>3.7</v>
+      </c>
       <c r="L48" s="1">
         <v>2.8</v>
       </c>
-      <c r="M48" s="1"/>
+      <c r="M48" s="1">
+        <v>2.8</v>
+      </c>
       <c r="N48" s="1">
         <v>3</v>
       </c>
-      <c r="O48" s="1"/>
+      <c r="O48" s="1">
+        <v>4.9000000000000004</v>
+      </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
@@ -3168,23 +3193,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3234,13 +3259,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3269,9 +3294,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3614,27 +3639,40 @@
       <c r="D84" s="1">
         <v>22</v>
       </c>
-      <c r="E84" s="1"/>
+      <c r="E84" s="1">
+        <f>27.3</f>
+        <v>27.3</v>
+      </c>
       <c r="F84" s="1">
         <v>6</v>
       </c>
-      <c r="G84" s="1"/>
+      <c r="G84" s="1">
+        <v>12.9</v>
+      </c>
       <c r="H84" s="1">
         <v>4.5</v>
       </c>
-      <c r="I84" s="1"/>
+      <c r="I84" s="1">
+        <v>15.7</v>
+      </c>
       <c r="J84" s="1">
         <v>5</v>
       </c>
-      <c r="K84" s="1"/>
+      <c r="K84" s="1">
+        <v>6.1</v>
+      </c>
       <c r="L84" s="1">
         <v>2.7</v>
       </c>
-      <c r="M84" s="1"/>
+      <c r="M84" s="1">
+        <v>6.3</v>
+      </c>
       <c r="N84" s="1">
         <v>2.5</v>
       </c>
-      <c r="O84" s="1"/>
+      <c r="O84" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
@@ -4502,6 +4540,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -4518,20 +4570,6 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A6E467-E67C-4A80-B411-6F5C7E6E8EF4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12BED02-0296-457A-B11A-605D8696E56B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -996,27 +996,39 @@
       <c r="D12" s="1">
         <v>45</v>
       </c>
-      <c r="E12" s="1"/>
+      <c r="E12" s="1">
+        <v>21.8</v>
+      </c>
       <c r="F12" s="1">
         <v>35.1</v>
       </c>
-      <c r="G12" s="1"/>
+      <c r="G12" s="1">
+        <v>31.8</v>
+      </c>
       <c r="H12" s="1">
         <v>30</v>
       </c>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1">
+        <v>31.7</v>
+      </c>
       <c r="J12" s="1">
         <v>12</v>
       </c>
-      <c r="K12" s="1"/>
+      <c r="K12" s="1">
+        <v>16.899999999999999</v>
+      </c>
       <c r="L12" s="1">
         <v>13.5</v>
       </c>
-      <c r="M12" s="1"/>
+      <c r="M12" s="1">
+        <v>11</v>
+      </c>
       <c r="N12" s="1">
         <v>5</v>
       </c>
-      <c r="O12" s="1"/>
+      <c r="O12" s="1">
+        <v>8.8000000000000007</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1847,23 +1859,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1913,13 +1925,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -1948,9 +1960,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2342,27 +2354,39 @@
       <c r="D49" s="1">
         <v>15</v>
       </c>
-      <c r="E49" s="1"/>
+      <c r="E49" s="1">
+        <v>35.9</v>
+      </c>
       <c r="F49" s="1">
         <v>10</v>
       </c>
-      <c r="G49" s="1"/>
+      <c r="G49" s="1">
+        <v>10.6</v>
+      </c>
       <c r="H49" s="1">
         <v>7.4</v>
       </c>
-      <c r="I49" s="1"/>
+      <c r="I49" s="1">
+        <v>10.5</v>
+      </c>
       <c r="J49" s="1">
         <v>5</v>
       </c>
-      <c r="K49" s="1"/>
+      <c r="K49" s="1">
+        <v>7.8</v>
+      </c>
       <c r="L49" s="1">
         <v>2.8</v>
       </c>
-      <c r="M49" s="1"/>
+      <c r="M49" s="1">
+        <v>7.4</v>
+      </c>
       <c r="N49" s="1">
         <v>3</v>
       </c>
-      <c r="O49" s="1"/>
+      <c r="O49" s="1">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
@@ -3193,23 +3217,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
-      <c r="N74" s="6"/>
-      <c r="O74" s="6"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3259,13 +3283,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3294,9 +3318,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3688,27 +3712,39 @@
       <c r="D85" s="1">
         <v>22</v>
       </c>
-      <c r="E85" s="1"/>
+      <c r="E85" s="1">
+        <v>24.8</v>
+      </c>
       <c r="F85" s="1">
         <v>6</v>
       </c>
-      <c r="G85" s="1"/>
+      <c r="G85" s="1">
+        <v>10.4</v>
+      </c>
       <c r="H85" s="1">
         <v>4.5</v>
       </c>
-      <c r="I85" s="1"/>
+      <c r="I85" s="1">
+        <v>21.9</v>
+      </c>
       <c r="J85" s="1">
         <v>5</v>
       </c>
-      <c r="K85" s="1"/>
+      <c r="K85" s="1">
+        <v>5.6</v>
+      </c>
       <c r="L85" s="1">
         <v>2.7</v>
       </c>
-      <c r="M85" s="1"/>
+      <c r="M85" s="1">
+        <v>5.5</v>
+      </c>
       <c r="N85" s="1">
         <v>2.5</v>
       </c>
-      <c r="O85" s="1"/>
+      <c r="O85" s="1">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
@@ -4540,20 +4576,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -4570,6 +4592,20 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12BED02-0296-457A-B11A-605D8696E56B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD09D62-AA11-4BBC-833A-E0CA13F24110}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -205,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1044,27 +1044,40 @@
       <c r="D13" s="1">
         <v>45</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="1">
+        <f>14.2+3*17.5</f>
+        <v>66.7</v>
+      </c>
       <c r="F13" s="1">
         <v>35.1</v>
       </c>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1">
+        <v>39.9</v>
+      </c>
       <c r="H13" s="1">
         <v>30</v>
       </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1">
+        <v>39.6</v>
+      </c>
       <c r="J13" s="1">
         <v>12</v>
       </c>
-      <c r="K13" s="1"/>
+      <c r="K13" s="1">
+        <v>14</v>
+      </c>
       <c r="L13" s="1">
         <v>13.5</v>
       </c>
-      <c r="M13" s="1"/>
+      <c r="M13" s="1">
+        <v>7.8</v>
+      </c>
       <c r="N13" s="1">
         <v>5</v>
       </c>
-      <c r="O13" s="1"/>
+      <c r="O13" s="1">
+        <v>8.4</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1859,23 +1872,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1925,13 +1938,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -1960,9 +1973,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2402,27 +2415,40 @@
       <c r="D50" s="1">
         <v>15</v>
       </c>
-      <c r="E50" s="1"/>
+      <c r="E50" s="1">
+        <f>28.5</f>
+        <v>28.5</v>
+      </c>
       <c r="F50" s="1">
         <v>10</v>
       </c>
-      <c r="G50" s="1"/>
+      <c r="G50" s="1">
+        <v>14.9</v>
+      </c>
       <c r="H50" s="1">
         <v>7.4</v>
       </c>
-      <c r="I50" s="1"/>
+      <c r="I50" s="1">
+        <v>8.6</v>
+      </c>
       <c r="J50" s="1">
         <v>5</v>
       </c>
-      <c r="K50" s="1"/>
+      <c r="K50" s="1">
+        <v>6.9</v>
+      </c>
       <c r="L50" s="1">
         <v>2.8</v>
       </c>
-      <c r="M50" s="1"/>
+      <c r="M50" s="1">
+        <v>6.8</v>
+      </c>
       <c r="N50" s="1">
         <v>3</v>
       </c>
-      <c r="O50" s="1"/>
+      <c r="O50" s="1">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
@@ -3217,23 +3243,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3283,13 +3309,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3318,9 +3344,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -3760,27 +3786,40 @@
       <c r="D86" s="1">
         <v>22</v>
       </c>
-      <c r="E86" s="1"/>
+      <c r="E86" s="1">
+        <f>17.2+15</f>
+        <v>32.200000000000003</v>
+      </c>
       <c r="F86" s="1">
         <v>6</v>
       </c>
-      <c r="G86" s="1"/>
+      <c r="G86" s="1">
+        <v>12.1</v>
+      </c>
       <c r="H86" s="1">
         <v>4.5</v>
       </c>
-      <c r="I86" s="1"/>
+      <c r="I86" s="1">
+        <v>20.399999999999999</v>
+      </c>
       <c r="J86" s="1">
         <v>5</v>
       </c>
-      <c r="K86" s="1"/>
+      <c r="K86" s="1">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="L86" s="1">
         <v>2.7</v>
       </c>
-      <c r="M86" s="1"/>
+      <c r="M86" s="1">
+        <v>7.3</v>
+      </c>
       <c r="N86" s="1">
         <v>2.5</v>
       </c>
-      <c r="O86" s="1"/>
+      <c r="O86" s="1">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
@@ -4576,6 +4615,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -4592,20 +4645,6 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD09D62-AA11-4BBC-833A-E0CA13F24110}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372E21C3-BE12-4C23-8744-7D965295A402}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -675,7 +675,7 @@
         <v>45.2</v>
       </c>
       <c r="J5" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K5" s="1">
         <v>10.5</v>
@@ -724,7 +724,7 @@
         <v>46.3</v>
       </c>
       <c r="J6" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K6" s="1">
         <v>7.9</v>
@@ -772,7 +772,7 @@
         <v>39.1</v>
       </c>
       <c r="J7" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K7" s="1">
         <v>12.2</v>
@@ -820,7 +820,7 @@
         <v>39.1</v>
       </c>
       <c r="J8" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K8" s="1">
         <v>12.3</v>
@@ -868,7 +868,7 @@
         <v>39.1</v>
       </c>
       <c r="J9" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K9" s="1">
         <v>12.3</v>
@@ -916,7 +916,7 @@
         <v>46.6</v>
       </c>
       <c r="J10" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K10" s="1">
         <v>9.4</v>
@@ -964,7 +964,7 @@
         <v>38.299999999999997</v>
       </c>
       <c r="J11" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K11" s="1">
         <v>7.5</v>
@@ -1012,7 +1012,7 @@
         <v>31.7</v>
       </c>
       <c r="J12" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K12" s="1">
         <v>16.899999999999999</v>
@@ -1061,7 +1061,7 @@
         <v>39.6</v>
       </c>
       <c r="J13" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K13" s="1">
         <v>14</v>
@@ -1093,27 +1093,39 @@
       <c r="D14" s="1">
         <v>45</v>
       </c>
-      <c r="E14" s="1"/>
+      <c r="E14" s="1">
+        <v>39.9</v>
+      </c>
       <c r="F14" s="1">
         <v>35.1</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1">
+        <v>30.6</v>
+      </c>
       <c r="H14" s="1">
         <v>30</v>
       </c>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1">
+        <v>33</v>
+      </c>
       <c r="J14" s="1">
-        <v>12</v>
-      </c>
-      <c r="K14" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="K14" s="1">
+        <v>12.6</v>
+      </c>
       <c r="L14" s="1">
         <v>13.5</v>
       </c>
-      <c r="M14" s="1"/>
+      <c r="M14" s="1">
+        <v>21</v>
+      </c>
       <c r="N14" s="1">
         <v>5</v>
       </c>
-      <c r="O14" s="1"/>
+      <c r="O14" s="1">
+        <v>7.1</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1129,27 +1141,39 @@
       <c r="D15" s="1">
         <v>45</v>
       </c>
-      <c r="E15" s="1"/>
+      <c r="E15" s="1">
+        <v>40.299999999999997</v>
+      </c>
       <c r="F15" s="1">
         <v>35.1</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1">
+        <v>30.7</v>
+      </c>
       <c r="H15" s="1">
         <v>30</v>
       </c>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1">
+        <v>33</v>
+      </c>
       <c r="J15" s="1">
-        <v>12</v>
-      </c>
-      <c r="K15" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="K15" s="1">
+        <v>12.6</v>
+      </c>
       <c r="L15" s="1">
         <v>13.5</v>
       </c>
-      <c r="M15" s="1"/>
+      <c r="M15" s="1">
+        <v>21</v>
+      </c>
       <c r="N15" s="1">
         <v>5</v>
       </c>
-      <c r="O15" s="1"/>
+      <c r="O15" s="1">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1165,27 +1189,40 @@
       <c r="D16" s="1">
         <v>45</v>
       </c>
-      <c r="E16" s="1"/>
+      <c r="E16" s="1">
+        <f>40.3+63</f>
+        <v>103.3</v>
+      </c>
       <c r="F16" s="1">
         <v>35.1</v>
       </c>
-      <c r="G16" s="1"/>
+      <c r="G16" s="1">
+        <v>30.7</v>
+      </c>
       <c r="H16" s="1">
         <v>30</v>
       </c>
-      <c r="I16" s="1"/>
+      <c r="I16" s="1">
+        <v>33.1</v>
+      </c>
       <c r="J16" s="1">
-        <v>12</v>
-      </c>
-      <c r="K16" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="K16" s="1">
+        <v>12.6</v>
+      </c>
       <c r="L16" s="1">
         <v>13.5</v>
       </c>
-      <c r="M16" s="1"/>
+      <c r="M16" s="1">
+        <v>21</v>
+      </c>
       <c r="N16" s="1">
         <v>5</v>
       </c>
-      <c r="O16" s="1"/>
+      <c r="O16" s="1">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1211,7 +1248,7 @@
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1">
@@ -1247,7 +1284,7 @@
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1">
@@ -1283,7 +1320,7 @@
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1">
@@ -1319,7 +1356,7 @@
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1">
@@ -1355,7 +1392,7 @@
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1">
@@ -1391,7 +1428,7 @@
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1">
@@ -1427,7 +1464,7 @@
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1">
@@ -1463,7 +1500,7 @@
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1">
@@ -1499,7 +1536,7 @@
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1">
@@ -1535,7 +1572,7 @@
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1">
@@ -1571,7 +1608,7 @@
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1">
@@ -1607,7 +1644,7 @@
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1">
@@ -1643,7 +1680,7 @@
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1">
@@ -1679,7 +1716,7 @@
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1">
@@ -1715,7 +1752,7 @@
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1">
@@ -1751,7 +1788,7 @@
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1">
@@ -1787,7 +1824,7 @@
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1">
@@ -1823,7 +1860,7 @@
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1">
@@ -1859,7 +1896,7 @@
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1">
@@ -2043,7 +2080,7 @@
         <v>11.9</v>
       </c>
       <c r="J42" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K42" s="1">
         <v>6.2</v>
@@ -2092,7 +2129,7 @@
         <v>19.8</v>
       </c>
       <c r="J43" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K43" s="1">
         <v>5.6</v>
@@ -2141,7 +2178,7 @@
         <v>17.899999999999999</v>
       </c>
       <c r="J44" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K44" s="1">
         <v>5.0999999999999996</v>
@@ -2189,7 +2226,7 @@
         <v>17.899999999999999</v>
       </c>
       <c r="J45" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K45" s="1">
         <v>5.0999999999999996</v>
@@ -2238,7 +2275,7 @@
         <v>17.899999999999999</v>
       </c>
       <c r="J46" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K46" s="1">
         <v>5.0999999999999996</v>
@@ -2286,7 +2323,7 @@
         <v>14.8</v>
       </c>
       <c r="J47" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K47" s="1">
         <v>4.2</v>
@@ -2335,7 +2372,7 @@
         <v>12.4</v>
       </c>
       <c r="J48" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K48" s="1">
         <v>3.7</v>
@@ -2383,7 +2420,7 @@
         <v>10.5</v>
       </c>
       <c r="J49" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K49" s="1">
         <v>7.8</v>
@@ -2432,7 +2469,7 @@
         <v>8.6</v>
       </c>
       <c r="J50" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K50" s="1">
         <v>6.9</v>
@@ -2464,27 +2501,40 @@
       <c r="D51" s="1">
         <v>15</v>
       </c>
-      <c r="E51" s="1"/>
+      <c r="E51" s="1">
+        <f>22.7</f>
+        <v>22.7</v>
+      </c>
       <c r="F51" s="1">
         <v>10</v>
       </c>
-      <c r="G51" s="1"/>
+      <c r="G51" s="1">
+        <v>10.7</v>
+      </c>
       <c r="H51" s="1">
         <v>7.4</v>
       </c>
-      <c r="I51" s="1"/>
+      <c r="I51" s="1">
+        <v>7.3</v>
+      </c>
       <c r="J51" s="1">
-        <v>5</v>
-      </c>
-      <c r="K51" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="K51" s="1">
+        <v>5.9</v>
+      </c>
       <c r="L51" s="1">
         <v>2.8</v>
       </c>
-      <c r="M51" s="1"/>
+      <c r="M51" s="1">
+        <v>5.3</v>
+      </c>
       <c r="N51" s="1">
         <v>3</v>
       </c>
-      <c r="O51" s="1"/>
+      <c r="O51" s="1">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
@@ -2500,27 +2550,39 @@
       <c r="D52" s="1">
         <v>15</v>
       </c>
-      <c r="E52" s="1"/>
+      <c r="E52" s="1">
+        <v>22.9</v>
+      </c>
       <c r="F52" s="1">
         <v>10</v>
       </c>
-      <c r="G52" s="1"/>
+      <c r="G52" s="1">
+        <v>10.7</v>
+      </c>
       <c r="H52" s="1">
         <v>7.4</v>
       </c>
-      <c r="I52" s="1"/>
+      <c r="I52" s="1">
+        <v>7.3</v>
+      </c>
       <c r="J52" s="1">
-        <v>5</v>
-      </c>
-      <c r="K52" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="K52" s="1">
+        <v>5.9</v>
+      </c>
       <c r="L52" s="1">
         <v>2.8</v>
       </c>
-      <c r="M52" s="1"/>
+      <c r="M52" s="1">
+        <v>5.3</v>
+      </c>
       <c r="N52" s="1">
         <v>3</v>
       </c>
-      <c r="O52" s="1"/>
+      <c r="O52" s="1">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
@@ -2536,27 +2598,40 @@
       <c r="D53" s="1">
         <v>15</v>
       </c>
-      <c r="E53" s="1"/>
+      <c r="E53" s="1">
+        <f>22.9+15</f>
+        <v>37.9</v>
+      </c>
       <c r="F53" s="1">
         <v>10</v>
       </c>
-      <c r="G53" s="1"/>
+      <c r="G53" s="1">
+        <v>10.7</v>
+      </c>
       <c r="H53" s="1">
         <v>7.4</v>
       </c>
-      <c r="I53" s="1"/>
+      <c r="I53" s="1">
+        <v>7.3</v>
+      </c>
       <c r="J53" s="1">
-        <v>5</v>
-      </c>
-      <c r="K53" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="K53" s="1">
+        <v>5.9</v>
+      </c>
       <c r="L53" s="1">
         <v>2.8</v>
       </c>
-      <c r="M53" s="1"/>
+      <c r="M53" s="1">
+        <v>5.3</v>
+      </c>
       <c r="N53" s="1">
         <v>3</v>
       </c>
-      <c r="O53" s="1"/>
+      <c r="O53" s="1">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
@@ -2582,7 +2657,7 @@
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1">
@@ -2618,7 +2693,7 @@
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1">
@@ -2654,7 +2729,7 @@
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1">
@@ -2690,7 +2765,7 @@
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K57" s="1"/>
       <c r="L57" s="1">
@@ -2726,7 +2801,7 @@
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1">
@@ -2762,7 +2837,7 @@
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1">
@@ -2798,7 +2873,7 @@
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1">
@@ -2834,7 +2909,7 @@
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K61" s="1"/>
       <c r="L61" s="1">
@@ -2870,7 +2945,7 @@
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="1">
@@ -2906,7 +2981,7 @@
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K63" s="1"/>
       <c r="L63" s="1">
@@ -2942,7 +3017,7 @@
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1">
@@ -2978,7 +3053,7 @@
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1">
@@ -3014,7 +3089,7 @@
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1">
@@ -3050,7 +3125,7 @@
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1">
@@ -3086,7 +3161,7 @@
       </c>
       <c r="I68" s="1"/>
       <c r="J68" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K68" s="1"/>
       <c r="L68" s="1">
@@ -3122,7 +3197,7 @@
       </c>
       <c r="I69" s="1"/>
       <c r="J69" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1">
@@ -3158,7 +3233,7 @@
       </c>
       <c r="I70" s="1"/>
       <c r="J70" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K70" s="1"/>
       <c r="L70" s="1">
@@ -3194,7 +3269,7 @@
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K71" s="1"/>
       <c r="L71" s="1">
@@ -3230,7 +3305,7 @@
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1">
@@ -3414,7 +3489,7 @@
         <v>12</v>
       </c>
       <c r="J78" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K78" s="1">
         <v>6.7</v>
@@ -3426,7 +3501,7 @@
         <v>10</v>
       </c>
       <c r="N78" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O78" s="1">
         <v>1.8</v>
@@ -3463,7 +3538,7 @@
         <v>21.2</v>
       </c>
       <c r="J79" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K79" s="1">
         <v>6.5</v>
@@ -3475,7 +3550,7 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="N79" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O79" s="1">
         <v>1.6</v>
@@ -3511,7 +3586,7 @@
         <v>19</v>
       </c>
       <c r="J80" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K80" s="1">
         <v>7.8</v>
@@ -3523,7 +3598,7 @@
         <v>8.4</v>
       </c>
       <c r="N80" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O80" s="1">
         <v>1.2</v>
@@ -3559,7 +3634,7 @@
         <v>19</v>
       </c>
       <c r="J81" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K81" s="1">
         <v>7.8</v>
@@ -3571,7 +3646,7 @@
         <v>8.4</v>
       </c>
       <c r="N81" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O81" s="1">
         <v>1.2</v>
@@ -3608,7 +3683,7 @@
         <v>19</v>
       </c>
       <c r="J82" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K82" s="1">
         <v>7.8</v>
@@ -3620,7 +3695,7 @@
         <v>8.4</v>
       </c>
       <c r="N82" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O82" s="1">
         <v>1.2</v>
@@ -3657,7 +3732,7 @@
         <v>16.899999999999999</v>
       </c>
       <c r="J83" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K83" s="1">
         <v>7.2</v>
@@ -3669,7 +3744,7 @@
         <v>7.9</v>
       </c>
       <c r="N83" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O83" s="1">
         <v>4.7</v>
@@ -3706,7 +3781,7 @@
         <v>15.7</v>
       </c>
       <c r="J84" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K84" s="1">
         <v>6.1</v>
@@ -3718,7 +3793,7 @@
         <v>6.3</v>
       </c>
       <c r="N84" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O84" s="1">
         <v>4</v>
@@ -3754,7 +3829,7 @@
         <v>21.9</v>
       </c>
       <c r="J85" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K85" s="1">
         <v>5.6</v>
@@ -3766,7 +3841,7 @@
         <v>5.5</v>
       </c>
       <c r="N85" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O85" s="1">
         <v>3.3</v>
@@ -3803,7 +3878,7 @@
         <v>20.399999999999999</v>
       </c>
       <c r="J86" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K86" s="1">
         <v>4.9000000000000004</v>
@@ -3815,7 +3890,7 @@
         <v>7.3</v>
       </c>
       <c r="N86" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O86" s="1">
         <v>3.2</v>
@@ -3835,27 +3910,40 @@
       <c r="D87" s="1">
         <v>22</v>
       </c>
-      <c r="E87" s="1"/>
+      <c r="E87" s="1">
+        <f>25.1</f>
+        <v>25.1</v>
+      </c>
       <c r="F87" s="1">
         <v>6</v>
       </c>
-      <c r="G87" s="1"/>
+      <c r="G87" s="1">
+        <v>11.1</v>
+      </c>
       <c r="H87" s="1">
         <v>4.5</v>
       </c>
-      <c r="I87" s="1"/>
+      <c r="I87" s="1">
+        <v>18.5</v>
+      </c>
       <c r="J87" s="1">
-        <v>5</v>
-      </c>
-      <c r="K87" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="K87" s="1">
+        <v>9.1</v>
+      </c>
       <c r="L87" s="1">
         <v>2.7</v>
       </c>
-      <c r="M87" s="1"/>
+      <c r="M87" s="1">
+        <v>6.5</v>
+      </c>
       <c r="N87" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="O87" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="O87" s="1">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
@@ -3871,27 +3959,39 @@
       <c r="D88" s="1">
         <v>22</v>
       </c>
-      <c r="E88" s="1"/>
+      <c r="E88" s="1">
+        <v>25.2</v>
+      </c>
       <c r="F88" s="1">
         <v>6</v>
       </c>
-      <c r="G88" s="1"/>
+      <c r="G88" s="1">
+        <v>11.1</v>
+      </c>
       <c r="H88" s="1">
         <v>4.5</v>
       </c>
-      <c r="I88" s="1"/>
+      <c r="I88" s="1">
+        <v>18.5</v>
+      </c>
       <c r="J88" s="1">
-        <v>5</v>
-      </c>
-      <c r="K88" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="K88" s="1">
+        <v>9.1</v>
+      </c>
       <c r="L88" s="1">
         <v>2.7</v>
       </c>
-      <c r="M88" s="1"/>
+      <c r="M88" s="1">
+        <v>6.5</v>
+      </c>
       <c r="N88" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="O88" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="O88" s="1">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
@@ -3907,27 +4007,39 @@
       <c r="D89" s="1">
         <v>22</v>
       </c>
-      <c r="E89" s="1"/>
+      <c r="E89" s="1">
+        <v>29</v>
+      </c>
       <c r="F89" s="1">
         <v>6</v>
       </c>
-      <c r="G89" s="1"/>
+      <c r="G89" s="1">
+        <v>11.1</v>
+      </c>
       <c r="H89" s="1">
         <v>4.5</v>
       </c>
-      <c r="I89" s="1"/>
+      <c r="I89" s="1">
+        <v>18.5</v>
+      </c>
       <c r="J89" s="1">
-        <v>5</v>
-      </c>
-      <c r="K89" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="K89" s="1">
+        <v>9.1</v>
+      </c>
       <c r="L89" s="1">
         <v>2.7</v>
       </c>
-      <c r="M89" s="1"/>
+      <c r="M89" s="1">
+        <v>6.5</v>
+      </c>
       <c r="N89" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="O89" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="O89" s="1">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
@@ -3953,7 +4065,7 @@
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K90" s="1"/>
       <c r="L90" s="1">
@@ -3961,7 +4073,7 @@
       </c>
       <c r="M90" s="1"/>
       <c r="N90" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O90" s="1"/>
     </row>
@@ -3989,7 +4101,7 @@
       </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K91" s="1"/>
       <c r="L91" s="1">
@@ -3997,7 +4109,7 @@
       </c>
       <c r="M91" s="1"/>
       <c r="N91" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O91" s="1"/>
     </row>
@@ -4025,7 +4137,7 @@
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1">
@@ -4033,7 +4145,7 @@
       </c>
       <c r="M92" s="1"/>
       <c r="N92" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O92" s="1"/>
     </row>
@@ -4061,7 +4173,7 @@
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K93" s="1"/>
       <c r="L93" s="1">
@@ -4069,7 +4181,7 @@
       </c>
       <c r="M93" s="1"/>
       <c r="N93" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O93" s="1"/>
     </row>
@@ -4097,7 +4209,7 @@
       </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K94" s="1"/>
       <c r="L94" s="1">
@@ -4105,7 +4217,7 @@
       </c>
       <c r="M94" s="1"/>
       <c r="N94" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O94" s="1"/>
     </row>
@@ -4133,7 +4245,7 @@
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K95" s="1"/>
       <c r="L95" s="1">
@@ -4141,7 +4253,7 @@
       </c>
       <c r="M95" s="1"/>
       <c r="N95" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O95" s="1"/>
     </row>
@@ -4169,7 +4281,7 @@
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K96" s="1"/>
       <c r="L96" s="1">
@@ -4177,7 +4289,7 @@
       </c>
       <c r="M96" s="1"/>
       <c r="N96" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O96" s="1"/>
     </row>
@@ -4205,7 +4317,7 @@
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K97" s="1"/>
       <c r="L97" s="1">
@@ -4213,7 +4325,7 @@
       </c>
       <c r="M97" s="1"/>
       <c r="N97" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O97" s="1"/>
     </row>
@@ -4241,7 +4353,7 @@
       </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K98" s="1"/>
       <c r="L98" s="1">
@@ -4249,7 +4361,7 @@
       </c>
       <c r="M98" s="1"/>
       <c r="N98" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O98" s="1"/>
     </row>
@@ -4277,7 +4389,7 @@
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K99" s="1"/>
       <c r="L99" s="1">
@@ -4285,7 +4397,7 @@
       </c>
       <c r="M99" s="1"/>
       <c r="N99" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O99" s="1"/>
     </row>
@@ -4313,7 +4425,7 @@
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K100" s="1"/>
       <c r="L100" s="1">
@@ -4321,7 +4433,7 @@
       </c>
       <c r="M100" s="1"/>
       <c r="N100" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O100" s="1"/>
     </row>
@@ -4349,7 +4461,7 @@
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1">
@@ -4357,7 +4469,7 @@
       </c>
       <c r="M101" s="1"/>
       <c r="N101" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O101" s="1"/>
     </row>
@@ -4385,7 +4497,7 @@
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K102" s="1"/>
       <c r="L102" s="1">
@@ -4393,7 +4505,7 @@
       </c>
       <c r="M102" s="1"/>
       <c r="N102" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O102" s="1"/>
     </row>
@@ -4421,7 +4533,7 @@
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K103" s="1"/>
       <c r="L103" s="1">
@@ -4429,7 +4541,7 @@
       </c>
       <c r="M103" s="1"/>
       <c r="N103" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O103" s="1"/>
     </row>
@@ -4457,7 +4569,7 @@
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K104" s="1"/>
       <c r="L104" s="1">
@@ -4465,7 +4577,7 @@
       </c>
       <c r="M104" s="1"/>
       <c r="N104" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O104" s="1"/>
     </row>
@@ -4493,7 +4605,7 @@
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K105" s="1"/>
       <c r="L105" s="1">
@@ -4501,7 +4613,7 @@
       </c>
       <c r="M105" s="1"/>
       <c r="N105" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O105" s="1"/>
     </row>
@@ -4529,7 +4641,7 @@
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1">
@@ -4537,7 +4649,7 @@
       </c>
       <c r="M106" s="1"/>
       <c r="N106" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O106" s="1"/>
     </row>
@@ -4565,7 +4677,7 @@
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K107" s="1"/>
       <c r="L107" s="1">
@@ -4573,7 +4685,7 @@
       </c>
       <c r="M107" s="1"/>
       <c r="N107" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O107" s="1"/>
     </row>
@@ -4601,7 +4713,7 @@
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K108" s="1"/>
       <c r="L108" s="1">
@@ -4609,7 +4721,7 @@
       </c>
       <c r="M108" s="1"/>
       <c r="N108" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O108" s="1"/>
     </row>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372E21C3-BE12-4C23-8744-7D965295A402}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957488F3-86C0-424C-A1C7-FCA8166668AF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -205,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1238,27 +1238,40 @@
       <c r="D17" s="1">
         <v>45</v>
       </c>
-      <c r="E17" s="1"/>
+      <c r="E17" s="1">
+        <f>70.8+17.8</f>
+        <v>88.6</v>
+      </c>
       <c r="F17" s="1">
         <v>35.1</v>
       </c>
-      <c r="G17" s="1"/>
+      <c r="G17" s="1">
+        <v>31.7</v>
+      </c>
       <c r="H17" s="1">
         <v>30</v>
       </c>
-      <c r="I17" s="1"/>
+      <c r="I17" s="1">
+        <v>44</v>
+      </c>
       <c r="J17" s="1">
         <v>6</v>
       </c>
-      <c r="K17" s="1"/>
+      <c r="K17" s="1">
+        <v>9</v>
+      </c>
       <c r="L17" s="1">
         <v>13.5</v>
       </c>
-      <c r="M17" s="1"/>
+      <c r="M17" s="1">
+        <v>18.899999999999999</v>
+      </c>
       <c r="N17" s="1">
         <v>5</v>
       </c>
-      <c r="O17" s="1"/>
+      <c r="O17" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1909,23 +1922,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1975,13 +1988,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2010,9 +2023,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2647,27 +2660,40 @@
       <c r="D54" s="1">
         <v>15</v>
       </c>
-      <c r="E54" s="1"/>
+      <c r="E54" s="1">
+        <f>32</f>
+        <v>32</v>
+      </c>
       <c r="F54" s="1">
         <v>10</v>
       </c>
-      <c r="G54" s="1"/>
+      <c r="G54" s="1">
+        <v>8.5</v>
+      </c>
       <c r="H54" s="1">
         <v>7.4</v>
       </c>
-      <c r="I54" s="1"/>
+      <c r="I54" s="1">
+        <v>10.1</v>
+      </c>
       <c r="J54" s="1">
         <v>3</v>
       </c>
-      <c r="K54" s="1"/>
+      <c r="K54" s="1">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="L54" s="1">
         <v>2.8</v>
       </c>
-      <c r="M54" s="1"/>
+      <c r="M54" s="1">
+        <v>4.7</v>
+      </c>
       <c r="N54" s="1">
         <v>3</v>
       </c>
-      <c r="O54" s="1"/>
+      <c r="O54" s="1">
+        <v>1.8</v>
+      </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -3318,23 +3344,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
-      <c r="N74" s="6"/>
-      <c r="O74" s="6"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3384,13 +3410,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3419,9 +3445,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -4055,27 +4081,40 @@
       <c r="D90" s="1">
         <v>22</v>
       </c>
-      <c r="E90" s="1"/>
+      <c r="E90" s="1">
+        <f>19+17</f>
+        <v>36</v>
+      </c>
       <c r="F90" s="1">
         <v>6</v>
       </c>
-      <c r="G90" s="1"/>
+      <c r="G90" s="1">
+        <v>10.4</v>
+      </c>
       <c r="H90" s="1">
         <v>4.5</v>
       </c>
-      <c r="I90" s="1"/>
+      <c r="I90" s="1">
+        <v>15.8</v>
+      </c>
       <c r="J90" s="1">
         <v>2</v>
       </c>
-      <c r="K90" s="1"/>
+      <c r="K90" s="1">
+        <v>8.1999999999999993</v>
+      </c>
       <c r="L90" s="1">
         <v>2.7</v>
       </c>
-      <c r="M90" s="1"/>
+      <c r="M90" s="1">
+        <v>6</v>
+      </c>
       <c r="N90" s="1">
         <v>2</v>
       </c>
-      <c r="O90" s="1"/>
+      <c r="O90" s="1">
+        <v>6.3</v>
+      </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
@@ -4727,20 +4766,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -4757,6 +4782,20 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957488F3-86C0-424C-A1C7-FCA8166668AF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12F5F3F-EBDB-4373-B2BE-3ABFE886D7CE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1287,27 +1287,40 @@
       <c r="D18" s="1">
         <v>45</v>
       </c>
-      <c r="E18" s="1"/>
+      <c r="E18" s="1">
+        <f>44.8</f>
+        <v>44.8</v>
+      </c>
       <c r="F18" s="1">
         <v>35.1</v>
       </c>
-      <c r="G18" s="1"/>
+      <c r="G18" s="1">
+        <v>32.5</v>
+      </c>
       <c r="H18" s="1">
         <v>30</v>
       </c>
-      <c r="I18" s="1"/>
+      <c r="I18" s="1">
+        <v>33.799999999999997</v>
+      </c>
       <c r="J18" s="1">
         <v>6</v>
       </c>
-      <c r="K18" s="1"/>
+      <c r="K18" s="1">
+        <v>11.1</v>
+      </c>
       <c r="L18" s="1">
         <v>13.5</v>
       </c>
-      <c r="M18" s="1"/>
+      <c r="M18" s="1">
+        <v>14.8</v>
+      </c>
       <c r="N18" s="1">
         <v>5</v>
       </c>
-      <c r="O18" s="1"/>
+      <c r="O18" s="1">
+        <v>9.3000000000000007</v>
+      </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -1922,23 +1935,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1988,13 +2001,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2023,9 +2036,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2709,27 +2722,40 @@
       <c r="D55" s="1">
         <v>15</v>
       </c>
-      <c r="E55" s="1"/>
+      <c r="E55" s="1">
+        <f>21.9+15</f>
+        <v>36.9</v>
+      </c>
       <c r="F55" s="1">
         <v>10</v>
       </c>
-      <c r="G55" s="1"/>
+      <c r="G55" s="1">
+        <v>13.8</v>
+      </c>
       <c r="H55" s="1">
         <v>7.4</v>
       </c>
-      <c r="I55" s="1"/>
+      <c r="I55" s="1">
+        <v>7.7</v>
+      </c>
       <c r="J55" s="1">
         <v>3</v>
       </c>
-      <c r="K55" s="1"/>
+      <c r="K55" s="1">
+        <v>3.4</v>
+      </c>
       <c r="L55" s="1">
         <v>2.8</v>
       </c>
-      <c r="M55" s="1"/>
+      <c r="M55" s="1">
+        <v>3.3</v>
+      </c>
       <c r="N55" s="1">
         <v>3</v>
       </c>
-      <c r="O55" s="1"/>
+      <c r="O55" s="1">
+        <v>1.1000000000000001</v>
+      </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
@@ -3344,23 +3370,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3410,13 +3436,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3445,9 +3471,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -4130,27 +4156,40 @@
       <c r="D91" s="1">
         <v>22</v>
       </c>
-      <c r="E91" s="1"/>
+      <c r="E91" s="1">
+        <f>28.1+11</f>
+        <v>39.1</v>
+      </c>
       <c r="F91" s="1">
         <v>6</v>
       </c>
-      <c r="G91" s="1"/>
+      <c r="G91" s="1">
+        <v>7.8</v>
+      </c>
       <c r="H91" s="1">
         <v>4.5</v>
       </c>
-      <c r="I91" s="1"/>
+      <c r="I91" s="1">
+        <v>16.8</v>
+      </c>
       <c r="J91" s="1">
         <v>2</v>
       </c>
-      <c r="K91" s="1"/>
+      <c r="K91" s="1">
+        <v>6.4</v>
+      </c>
       <c r="L91" s="1">
         <v>2.7</v>
       </c>
-      <c r="M91" s="1"/>
+      <c r="M91" s="1">
+        <v>4.7</v>
+      </c>
       <c r="N91" s="1">
         <v>2</v>
       </c>
-      <c r="O91" s="1"/>
+      <c r="O91" s="1">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
@@ -4766,6 +4805,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -4782,20 +4835,6 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12F5F3F-EBDB-4373-B2BE-3ABFE886D7CE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E340865-A652-4F93-8F02-9059069F470A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1336,27 +1336,40 @@
       <c r="D19" s="1">
         <v>45</v>
       </c>
-      <c r="E19" s="1"/>
+      <c r="E19" s="1">
+        <f>23.7+33</f>
+        <v>56.7</v>
+      </c>
       <c r="F19" s="1">
         <v>35.1</v>
       </c>
-      <c r="G19" s="1"/>
+      <c r="G19" s="1">
+        <v>51.7</v>
+      </c>
       <c r="H19" s="1">
         <v>30</v>
       </c>
-      <c r="I19" s="1"/>
+      <c r="I19" s="1">
+        <v>26.4</v>
+      </c>
       <c r="J19" s="1">
         <v>6</v>
       </c>
-      <c r="K19" s="1"/>
+      <c r="K19" s="1">
+        <v>7.8</v>
+      </c>
       <c r="L19" s="1">
         <v>13.5</v>
       </c>
-      <c r="M19" s="1"/>
+      <c r="M19" s="1">
+        <v>16.8</v>
+      </c>
       <c r="N19" s="1">
         <v>5</v>
       </c>
-      <c r="O19" s="1"/>
+      <c r="O19" s="1">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -2771,27 +2784,40 @@
       <c r="D56" s="1">
         <v>15</v>
       </c>
-      <c r="E56" s="1"/>
+      <c r="E56" s="1">
+        <f>28.1</f>
+        <v>28.1</v>
+      </c>
       <c r="F56" s="1">
         <v>10</v>
       </c>
-      <c r="G56" s="1"/>
+      <c r="G56" s="1">
+        <v>11.6</v>
+      </c>
       <c r="H56" s="1">
         <v>7.4</v>
       </c>
-      <c r="I56" s="1"/>
+      <c r="I56" s="1">
+        <v>6.3</v>
+      </c>
       <c r="J56" s="1">
         <v>3</v>
       </c>
-      <c r="K56" s="1"/>
+      <c r="K56" s="1">
+        <v>2.8</v>
+      </c>
       <c r="L56" s="1">
         <v>2.8</v>
       </c>
-      <c r="M56" s="1"/>
+      <c r="M56" s="1">
+        <v>1.6</v>
+      </c>
       <c r="N56" s="1">
         <v>3</v>
       </c>
-      <c r="O56" s="1"/>
+      <c r="O56" s="1">
+        <v>7.6</v>
+      </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
@@ -4205,27 +4231,40 @@
       <c r="D92" s="1">
         <v>22</v>
       </c>
-      <c r="E92" s="1"/>
+      <c r="E92" s="1">
+        <f>33.8+0.4</f>
+        <v>34.199999999999996</v>
+      </c>
       <c r="F92" s="1">
         <v>6</v>
       </c>
-      <c r="G92" s="1"/>
+      <c r="G92" s="1">
+        <v>6.5</v>
+      </c>
       <c r="H92" s="1">
         <v>4.5</v>
       </c>
-      <c r="I92" s="1"/>
+      <c r="I92" s="1">
+        <v>16.100000000000001</v>
+      </c>
       <c r="J92" s="1">
         <v>2</v>
       </c>
-      <c r="K92" s="1"/>
+      <c r="K92" s="1">
+        <v>5.8</v>
+      </c>
       <c r="L92" s="1">
         <v>2.7</v>
       </c>
-      <c r="M92" s="1"/>
+      <c r="M92" s="1">
+        <v>6.5</v>
+      </c>
       <c r="N92" s="1">
         <v>2</v>
       </c>
-      <c r="O92" s="1"/>
+      <c r="O92" s="1">
+        <v>4.5999999999999996</v>
+      </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E340865-A652-4F93-8F02-9059069F470A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8BAAB5-2D85-48E8-BA2F-86142C758EEB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1385,27 +1385,40 @@
       <c r="D20" s="1">
         <v>45</v>
       </c>
-      <c r="E20" s="1"/>
+      <c r="E20" s="1">
+        <f>35.5+17.5</f>
+        <v>53</v>
+      </c>
       <c r="F20" s="1">
         <v>35.1</v>
       </c>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1">
+        <v>43.1</v>
+      </c>
       <c r="H20" s="1">
         <v>30</v>
       </c>
-      <c r="I20" s="1"/>
+      <c r="I20" s="1">
+        <v>16.2</v>
+      </c>
       <c r="J20" s="1">
         <v>6</v>
       </c>
-      <c r="K20" s="1"/>
+      <c r="K20" s="1">
+        <v>5.2</v>
+      </c>
       <c r="L20" s="1">
         <v>13.5</v>
       </c>
-      <c r="M20" s="1"/>
+      <c r="M20" s="1">
+        <v>14</v>
+      </c>
       <c r="N20" s="1">
         <v>5</v>
       </c>
-      <c r="O20" s="1"/>
+      <c r="O20" s="1">
+        <v>10.199999999999999</v>
+      </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -1948,23 +1961,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -2014,13 +2027,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2049,9 +2062,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2833,27 +2846,39 @@
       <c r="D57" s="1">
         <v>15</v>
       </c>
-      <c r="E57" s="1"/>
+      <c r="E57" s="1">
+        <v>36.6</v>
+      </c>
       <c r="F57" s="1">
         <v>10</v>
       </c>
-      <c r="G57" s="1"/>
+      <c r="G57" s="1">
+        <v>10.199999999999999</v>
+      </c>
       <c r="H57" s="1">
         <v>7.4</v>
       </c>
-      <c r="I57" s="1"/>
+      <c r="I57" s="1">
+        <v>4.7</v>
+      </c>
       <c r="J57" s="1">
         <v>3</v>
       </c>
-      <c r="K57" s="1"/>
+      <c r="K57" s="1">
+        <v>1.6</v>
+      </c>
       <c r="L57" s="1">
         <v>2.8</v>
       </c>
-      <c r="M57" s="1"/>
+      <c r="M57" s="1">
+        <v>1.3</v>
+      </c>
       <c r="N57" s="1">
         <v>3</v>
       </c>
-      <c r="O57" s="1"/>
+      <c r="O57" s="1">
+        <v>7</v>
+      </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
@@ -3396,23 +3421,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
-      <c r="N74" s="6"/>
-      <c r="O74" s="6"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3462,13 +3487,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3497,9 +3522,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -4280,27 +4305,40 @@
       <c r="D93" s="1">
         <v>22</v>
       </c>
-      <c r="E93" s="1"/>
+      <c r="E93" s="1">
+        <f>27.4+6</f>
+        <v>33.4</v>
+      </c>
       <c r="F93" s="1">
         <v>6</v>
       </c>
-      <c r="G93" s="1"/>
+      <c r="G93" s="1">
+        <v>5.2</v>
+      </c>
       <c r="H93" s="1">
         <v>4.5</v>
       </c>
-      <c r="I93" s="1"/>
+      <c r="I93" s="1">
+        <v>15.1</v>
+      </c>
       <c r="J93" s="1">
         <v>2</v>
       </c>
-      <c r="K93" s="1"/>
+      <c r="K93" s="1">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="L93" s="1">
         <v>2.7</v>
       </c>
-      <c r="M93" s="1"/>
+      <c r="M93" s="1">
+        <v>6.1</v>
+      </c>
       <c r="N93" s="1">
         <v>2</v>
       </c>
-      <c r="O93" s="1"/>
+      <c r="O93" s="1">
+        <v>4.5999999999999996</v>
+      </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
@@ -4844,20 +4882,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -4874,6 +4898,20 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8BAAB5-2D85-48E8-BA2F-86142C758EEB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64C34FE-A7AA-457D-ACB7-F3ACB5692378}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="22">
   <si>
     <t>№ п/п</t>
   </si>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t>МАРИУПОЛЬ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -205,14 +208,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +507,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +573,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +608,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1434,27 +1437,39 @@
       <c r="D21" s="1">
         <v>45</v>
       </c>
-      <c r="E21" s="1"/>
+      <c r="E21" s="1">
+        <v>29.6</v>
+      </c>
       <c r="F21" s="1">
         <v>35.1</v>
       </c>
-      <c r="G21" s="1"/>
+      <c r="G21" s="1">
+        <v>35.1</v>
+      </c>
       <c r="H21" s="1">
         <v>30</v>
       </c>
-      <c r="I21" s="1"/>
+      <c r="I21" s="1">
+        <v>26.7</v>
+      </c>
       <c r="J21" s="1">
         <v>6</v>
       </c>
-      <c r="K21" s="1"/>
+      <c r="K21" s="1">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L21" s="1">
         <v>13.5</v>
       </c>
-      <c r="M21" s="1"/>
+      <c r="M21" s="1">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="N21" s="1">
         <v>5</v>
       </c>
-      <c r="O21" s="1"/>
+      <c r="O21" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -1470,27 +1485,39 @@
       <c r="D22" s="1">
         <v>45</v>
       </c>
-      <c r="E22" s="1"/>
+      <c r="E22" s="1">
+        <v>30.4</v>
+      </c>
       <c r="F22" s="1">
         <v>35.1</v>
       </c>
-      <c r="G22" s="1"/>
+      <c r="G22" s="1">
+        <v>36</v>
+      </c>
       <c r="H22" s="1">
         <v>30</v>
       </c>
-      <c r="I22" s="1"/>
+      <c r="I22" s="1">
+        <v>26.8</v>
+      </c>
       <c r="J22" s="1">
         <v>6</v>
       </c>
-      <c r="K22" s="1"/>
+      <c r="K22" s="1">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L22" s="1">
         <v>13.5</v>
       </c>
-      <c r="M22" s="1"/>
+      <c r="M22" s="1">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="N22" s="1">
         <v>5</v>
       </c>
-      <c r="O22" s="1"/>
+      <c r="O22" s="1">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -1506,27 +1533,40 @@
       <c r="D23" s="1">
         <v>45</v>
       </c>
-      <c r="E23" s="1"/>
+      <c r="E23" s="1">
+        <f>30.4+35</f>
+        <v>65.400000000000006</v>
+      </c>
       <c r="F23" s="1">
         <v>35.1</v>
       </c>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1">
+        <v>36</v>
+      </c>
       <c r="H23" s="1">
         <v>30</v>
       </c>
-      <c r="I23" s="1"/>
+      <c r="I23" s="1">
+        <v>26.8</v>
+      </c>
       <c r="J23" s="1">
         <v>6</v>
       </c>
-      <c r="K23" s="1"/>
+      <c r="K23" s="1">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L23" s="1">
         <v>13.5</v>
       </c>
-      <c r="M23" s="1"/>
+      <c r="M23" s="1">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="N23" s="1">
         <v>5</v>
       </c>
-      <c r="O23" s="1"/>
+      <c r="O23" s="1">
+        <v>9.1999999999999993</v>
+      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1562,7 +1602,9 @@
       <c r="N24" s="1">
         <v>5</v>
       </c>
-      <c r="O24" s="1"/>
+      <c r="O24" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -1961,23 +2003,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -2027,13 +2069,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2062,9 +2104,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -2894,27 +2936,39 @@
       <c r="D58" s="1">
         <v>15</v>
       </c>
-      <c r="E58" s="1"/>
+      <c r="E58" s="1">
+        <v>31.1</v>
+      </c>
       <c r="F58" s="1">
         <v>10</v>
       </c>
-      <c r="G58" s="1"/>
+      <c r="G58" s="1">
+        <v>17.3</v>
+      </c>
       <c r="H58" s="1">
         <v>7.4</v>
       </c>
-      <c r="I58" s="1"/>
+      <c r="I58" s="1">
+        <v>3</v>
+      </c>
       <c r="J58" s="1">
         <v>3</v>
       </c>
-      <c r="K58" s="1"/>
+      <c r="K58" s="1">
+        <v>1.3</v>
+      </c>
       <c r="L58" s="1">
         <v>2.8</v>
       </c>
-      <c r="M58" s="1"/>
+      <c r="M58" s="1">
+        <v>0.8</v>
+      </c>
       <c r="N58" s="1">
         <v>3</v>
       </c>
-      <c r="O58" s="1"/>
+      <c r="O58" s="1">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
@@ -2930,27 +2984,39 @@
       <c r="D59" s="1">
         <v>15</v>
       </c>
-      <c r="E59" s="1"/>
+      <c r="E59" s="1">
+        <v>31.6</v>
+      </c>
       <c r="F59" s="1">
         <v>10</v>
       </c>
-      <c r="G59" s="1"/>
+      <c r="G59" s="1">
+        <v>17.100000000000001</v>
+      </c>
       <c r="H59" s="1">
         <v>7.4</v>
       </c>
-      <c r="I59" s="1"/>
+      <c r="I59" s="1">
+        <v>3</v>
+      </c>
       <c r="J59" s="1">
         <v>3</v>
       </c>
-      <c r="K59" s="1"/>
+      <c r="K59" s="1">
+        <v>1.3</v>
+      </c>
       <c r="L59" s="1">
         <v>2.8</v>
       </c>
-      <c r="M59" s="1"/>
+      <c r="M59" s="1">
+        <v>0.8</v>
+      </c>
       <c r="N59" s="1">
         <v>3</v>
       </c>
-      <c r="O59" s="1"/>
+      <c r="O59" s="1">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
@@ -2966,27 +3032,39 @@
       <c r="D60" s="1">
         <v>15</v>
       </c>
-      <c r="E60" s="1"/>
+      <c r="E60" s="1">
+        <v>31.6</v>
+      </c>
       <c r="F60" s="1">
         <v>10</v>
       </c>
-      <c r="G60" s="1"/>
+      <c r="G60" s="1">
+        <v>17.100000000000001</v>
+      </c>
       <c r="H60" s="1">
         <v>7.4</v>
       </c>
-      <c r="I60" s="1"/>
+      <c r="I60" s="1">
+        <v>3</v>
+      </c>
       <c r="J60" s="1">
         <v>3</v>
       </c>
-      <c r="K60" s="1"/>
+      <c r="K60" s="1">
+        <v>1.3</v>
+      </c>
       <c r="L60" s="1">
         <v>2.8</v>
       </c>
-      <c r="M60" s="1"/>
+      <c r="M60" s="1">
+        <v>0.8</v>
+      </c>
       <c r="N60" s="1">
         <v>3</v>
       </c>
-      <c r="O60" s="1"/>
+      <c r="O60" s="1">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
@@ -3421,23 +3499,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3487,13 +3565,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3522,9 +3600,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -4354,27 +4432,39 @@
       <c r="D94" s="1">
         <v>22</v>
       </c>
-      <c r="E94" s="1"/>
+      <c r="E94" s="1">
+        <v>21.9</v>
+      </c>
       <c r="F94" s="1">
         <v>6</v>
       </c>
-      <c r="G94" s="1"/>
+      <c r="G94" s="1">
+        <v>11.7</v>
+      </c>
       <c r="H94" s="1">
         <v>4.5</v>
       </c>
-      <c r="I94" s="1"/>
+      <c r="I94" s="1">
+        <v>12</v>
+      </c>
       <c r="J94" s="1">
         <v>2</v>
       </c>
-      <c r="K94" s="1"/>
+      <c r="K94" s="1">
+        <v>5.4</v>
+      </c>
       <c r="L94" s="1">
         <v>2.7</v>
       </c>
-      <c r="M94" s="1"/>
+      <c r="M94" s="1">
+        <v>5.3</v>
+      </c>
       <c r="N94" s="1">
         <v>2</v>
       </c>
-      <c r="O94" s="1"/>
+      <c r="O94" s="1">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
@@ -4390,27 +4480,39 @@
       <c r="D95" s="1">
         <v>22</v>
       </c>
-      <c r="E95" s="1"/>
+      <c r="E95" s="1">
+        <v>22.2</v>
+      </c>
       <c r="F95" s="1">
         <v>6</v>
       </c>
-      <c r="G95" s="1"/>
+      <c r="G95" s="1">
+        <v>10.1</v>
+      </c>
       <c r="H95" s="1">
         <v>4.5</v>
       </c>
-      <c r="I95" s="1"/>
+      <c r="I95" s="1">
+        <v>12</v>
+      </c>
       <c r="J95" s="1">
         <v>2</v>
       </c>
-      <c r="K95" s="1"/>
+      <c r="K95" s="1">
+        <v>5.4</v>
+      </c>
       <c r="L95" s="1">
         <v>2.7</v>
       </c>
-      <c r="M95" s="1"/>
+      <c r="M95" s="1">
+        <v>5.3</v>
+      </c>
       <c r="N95" s="1">
         <v>2</v>
       </c>
-      <c r="O95" s="1"/>
+      <c r="O95" s="1">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
@@ -4426,27 +4528,40 @@
       <c r="D96" s="1">
         <v>22</v>
       </c>
-      <c r="E96" s="1"/>
+      <c r="E96" s="1">
+        <f>42.6</f>
+        <v>42.6</v>
+      </c>
       <c r="F96" s="1">
         <v>6</v>
       </c>
-      <c r="G96" s="1"/>
+      <c r="G96" s="1">
+        <v>10.1</v>
+      </c>
       <c r="H96" s="1">
         <v>4.5</v>
       </c>
-      <c r="I96" s="1"/>
+      <c r="I96" s="1">
+        <v>12</v>
+      </c>
       <c r="J96" s="1">
         <v>2</v>
       </c>
-      <c r="K96" s="1"/>
+      <c r="K96" s="1">
+        <v>5.4</v>
+      </c>
       <c r="L96" s="1">
         <v>2.7</v>
       </c>
-      <c r="M96" s="1"/>
+      <c r="M96" s="1">
+        <v>5.3</v>
+      </c>
       <c r="N96" s="1">
         <v>2</v>
       </c>
-      <c r="O96" s="1"/>
+      <c r="O96" s="1">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
@@ -4882,6 +4997,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -4898,20 +5027,6 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64C34FE-A7AA-457D-ACB7-F3ACB5692378}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933DC3E9-CF29-42BF-9D19-9B9DA3D742CA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="21">
   <si>
     <t>№ п/п</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>МАРИУПОЛЬ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1582,28 +1579,39 @@
       <c r="D24" s="1">
         <v>45</v>
       </c>
-      <c r="E24" s="1"/>
+      <c r="E24" s="1">
+        <f>53.8</f>
+        <v>53.8</v>
+      </c>
       <c r="F24" s="1">
         <v>35.1</v>
       </c>
-      <c r="G24" s="1"/>
+      <c r="G24" s="1">
+        <v>37.799999999999997</v>
+      </c>
       <c r="H24" s="1">
         <v>30</v>
       </c>
-      <c r="I24" s="1"/>
+      <c r="I24" s="1">
+        <v>33.5</v>
+      </c>
       <c r="J24" s="1">
         <v>6</v>
       </c>
-      <c r="K24" s="1"/>
+      <c r="K24" s="1">
+        <v>9.6</v>
+      </c>
       <c r="L24" s="1">
         <v>13.5</v>
       </c>
-      <c r="M24" s="1"/>
+      <c r="M24" s="1">
+        <v>11.7</v>
+      </c>
       <c r="N24" s="1">
         <v>5</v>
       </c>
-      <c r="O24" s="1" t="s">
-        <v>21</v>
+      <c r="O24" s="1">
+        <v>7.8</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -3080,27 +3088,40 @@
       <c r="D61" s="1">
         <v>15</v>
       </c>
-      <c r="E61" s="1"/>
+      <c r="E61" s="1">
+        <f>24.5+15</f>
+        <v>39.5</v>
+      </c>
       <c r="F61" s="1">
         <v>10</v>
       </c>
-      <c r="G61" s="1"/>
+      <c r="G61" s="1">
+        <v>14.9</v>
+      </c>
       <c r="H61" s="1">
         <v>7.4</v>
       </c>
-      <c r="I61" s="1"/>
+      <c r="I61" s="1">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="J61" s="1">
         <v>3</v>
       </c>
-      <c r="K61" s="1"/>
+      <c r="K61" s="1">
+        <v>1</v>
+      </c>
       <c r="L61" s="1">
         <v>2.8</v>
       </c>
-      <c r="M61" s="1"/>
+      <c r="M61" s="1">
+        <v>6.4</v>
+      </c>
       <c r="N61" s="1">
         <v>3</v>
       </c>
-      <c r="O61" s="1"/>
+      <c r="O61" s="1">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
@@ -4577,27 +4598,40 @@
       <c r="D97" s="1">
         <v>22</v>
       </c>
-      <c r="E97" s="1"/>
+      <c r="E97" s="1">
+        <f>34.2+1</f>
+        <v>35.200000000000003</v>
+      </c>
       <c r="F97" s="1">
         <v>6</v>
       </c>
-      <c r="G97" s="1"/>
+      <c r="G97" s="1">
+        <v>12.1</v>
+      </c>
       <c r="H97" s="1">
         <v>4.5</v>
       </c>
-      <c r="I97" s="1"/>
+      <c r="I97" s="1">
+        <v>10.3</v>
+      </c>
       <c r="J97" s="1">
         <v>2</v>
       </c>
-      <c r="K97" s="1"/>
+      <c r="K97" s="1">
+        <v>4.7</v>
+      </c>
       <c r="L97" s="1">
         <v>2.7</v>
       </c>
-      <c r="M97" s="1"/>
+      <c r="M97" s="1">
+        <v>4.7</v>
+      </c>
       <c r="N97" s="1">
         <v>2</v>
       </c>
-      <c r="O97" s="1"/>
+      <c r="O97" s="1">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933DC3E9-CF29-42BF-9D19-9B9DA3D742CA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D16691A-A1A1-41CC-92C6-2DEEFFF30302}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1628,27 +1628,40 @@
       <c r="D25" s="1">
         <v>45</v>
       </c>
-      <c r="E25" s="1"/>
+      <c r="E25" s="1">
+        <f>29.7</f>
+        <v>29.7</v>
+      </c>
       <c r="F25" s="1">
         <v>35.1</v>
       </c>
-      <c r="G25" s="1"/>
+      <c r="G25" s="1">
+        <v>26.6</v>
+      </c>
       <c r="H25" s="1">
         <v>30</v>
       </c>
-      <c r="I25" s="1"/>
+      <c r="I25" s="1">
+        <v>24</v>
+      </c>
       <c r="J25" s="1">
         <v>6</v>
       </c>
-      <c r="K25" s="1"/>
+      <c r="K25" s="1">
+        <v>7.5</v>
+      </c>
       <c r="L25" s="1">
         <v>13.5</v>
       </c>
-      <c r="M25" s="1"/>
+      <c r="M25" s="1">
+        <v>7</v>
+      </c>
       <c r="N25" s="1">
         <v>5</v>
       </c>
-      <c r="O25" s="1"/>
+      <c r="O25" s="1">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -2011,23 +2024,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -2077,13 +2090,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2112,9 +2125,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -3137,27 +3150,40 @@
       <c r="D62" s="1">
         <v>15</v>
       </c>
-      <c r="E62" s="1"/>
+      <c r="E62" s="1">
+        <f>30.3</f>
+        <v>30.3</v>
+      </c>
       <c r="F62" s="1">
         <v>10</v>
       </c>
-      <c r="G62" s="1"/>
+      <c r="G62" s="1">
+        <v>12</v>
+      </c>
       <c r="H62" s="1">
         <v>7.4</v>
       </c>
-      <c r="I62" s="1"/>
+      <c r="I62" s="1">
+        <v>11.2</v>
+      </c>
       <c r="J62" s="1">
         <v>3</v>
       </c>
-      <c r="K62" s="1"/>
+      <c r="K62" s="1">
+        <v>5.9</v>
+      </c>
       <c r="L62" s="1">
         <v>2.8</v>
       </c>
-      <c r="M62" s="1"/>
+      <c r="M62" s="1">
+        <v>5.3</v>
+      </c>
       <c r="N62" s="1">
         <v>3</v>
       </c>
-      <c r="O62" s="1"/>
+      <c r="O62" s="1">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
@@ -3520,23 +3546,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
-      <c r="N74" s="6"/>
-      <c r="O74" s="6"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3586,13 +3612,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3621,9 +3647,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -4647,27 +4673,40 @@
       <c r="D98" s="1">
         <v>22</v>
       </c>
-      <c r="E98" s="1"/>
+      <c r="E98" s="1">
+        <f>30+11</f>
+        <v>41</v>
+      </c>
       <c r="F98" s="1">
         <v>6</v>
       </c>
-      <c r="G98" s="1"/>
+      <c r="G98" s="1">
+        <v>12.7</v>
+      </c>
       <c r="H98" s="1">
         <v>4.5</v>
       </c>
-      <c r="I98" s="1"/>
+      <c r="I98" s="1">
+        <v>9.1</v>
+      </c>
       <c r="J98" s="1">
         <v>2</v>
       </c>
-      <c r="K98" s="1"/>
+      <c r="K98" s="1">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L98" s="1">
         <v>2.7</v>
       </c>
-      <c r="M98" s="1"/>
+      <c r="M98" s="1">
+        <v>10.3</v>
+      </c>
       <c r="N98" s="1">
         <v>2</v>
       </c>
-      <c r="O98" s="1"/>
+      <c r="O98" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
@@ -5031,20 +5070,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -5061,6 +5086,20 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D16691A-A1A1-41CC-92C6-2DEEFFF30302}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30402C5-3F66-438B-A1A2-88A1C8D712B3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1677,27 +1677,40 @@
       <c r="D26" s="1">
         <v>45</v>
       </c>
-      <c r="E26" s="1"/>
+      <c r="E26" s="1">
+        <f>11.8+17.5</f>
+        <v>29.3</v>
+      </c>
       <c r="F26" s="1">
         <v>35.1</v>
       </c>
-      <c r="G26" s="1"/>
+      <c r="G26" s="1">
+        <v>19.100000000000001</v>
+      </c>
       <c r="H26" s="1">
         <v>30</v>
       </c>
-      <c r="I26" s="1"/>
+      <c r="I26" s="1">
+        <v>17.7</v>
+      </c>
       <c r="J26" s="1">
         <v>6</v>
       </c>
-      <c r="K26" s="1"/>
+      <c r="K26" s="1">
+        <v>9.4</v>
+      </c>
       <c r="L26" s="1">
         <v>13.5</v>
       </c>
-      <c r="M26" s="1"/>
+      <c r="M26" s="1">
+        <v>13.5</v>
+      </c>
       <c r="N26" s="1">
         <v>5</v>
       </c>
-      <c r="O26" s="1"/>
+      <c r="O26" s="1">
+        <v>4.0999999999999996</v>
+      </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -2024,23 +2037,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -2090,13 +2103,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2125,9 +2138,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -3199,27 +3212,40 @@
       <c r="D63" s="1">
         <v>15</v>
       </c>
-      <c r="E63" s="1"/>
+      <c r="E63" s="1">
+        <f>22.9+15</f>
+        <v>37.9</v>
+      </c>
       <c r="F63" s="1">
         <v>10</v>
       </c>
-      <c r="G63" s="1"/>
+      <c r="G63" s="1">
+        <v>10.5</v>
+      </c>
       <c r="H63" s="1">
         <v>7.4</v>
       </c>
-      <c r="I63" s="1"/>
+      <c r="I63" s="1">
+        <v>18.899999999999999</v>
+      </c>
       <c r="J63" s="1">
         <v>3</v>
       </c>
-      <c r="K63" s="1"/>
+      <c r="K63" s="1">
+        <v>6</v>
+      </c>
       <c r="L63" s="1">
         <v>2.8</v>
       </c>
-      <c r="M63" s="1"/>
+      <c r="M63" s="1">
+        <v>4.4000000000000004</v>
+      </c>
       <c r="N63" s="1">
         <v>3</v>
       </c>
-      <c r="O63" s="1"/>
+      <c r="O63" s="1">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
@@ -3546,23 +3572,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3612,13 +3638,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3647,9 +3673,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -4722,27 +4748,40 @@
       <c r="D99" s="1">
         <v>22</v>
       </c>
-      <c r="E99" s="1"/>
+      <c r="E99" s="1">
+        <f>36.1</f>
+        <v>36.1</v>
+      </c>
       <c r="F99" s="1">
         <v>6</v>
       </c>
-      <c r="G99" s="1"/>
+      <c r="G99" s="1">
+        <v>11.2</v>
+      </c>
       <c r="H99" s="1">
         <v>4.5</v>
       </c>
-      <c r="I99" s="1"/>
+      <c r="I99" s="1">
+        <v>8.1999999999999993</v>
+      </c>
       <c r="J99" s="1">
         <v>2</v>
       </c>
-      <c r="K99" s="1"/>
+      <c r="K99" s="1">
+        <v>3.1</v>
+      </c>
       <c r="L99" s="1">
         <v>2.7</v>
       </c>
-      <c r="M99" s="1"/>
+      <c r="M99" s="1">
+        <v>3.2</v>
+      </c>
       <c r="N99" s="1">
         <v>2</v>
       </c>
-      <c r="O99" s="1"/>
+      <c r="O99" s="1">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
@@ -5070,6 +5109,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -5086,20 +5139,6 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30402C5-3F66-438B-A1A2-88A1C8D712B3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D36825-704C-401B-88EE-D21A216083E5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1726,27 +1726,40 @@
       <c r="D27" s="1">
         <v>45</v>
       </c>
-      <c r="E27" s="1"/>
+      <c r="E27" s="1">
+        <f>27.7</f>
+        <v>27.7</v>
+      </c>
       <c r="F27" s="1">
         <v>35.1</v>
       </c>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1">
+        <v>27.1</v>
+      </c>
       <c r="H27" s="1">
         <v>30</v>
       </c>
-      <c r="I27" s="1"/>
+      <c r="I27" s="1">
+        <v>9.1999999999999993</v>
+      </c>
       <c r="J27" s="1">
         <v>6</v>
       </c>
-      <c r="K27" s="1"/>
+      <c r="K27" s="1">
+        <v>6.5</v>
+      </c>
       <c r="L27" s="1">
         <v>13.5</v>
       </c>
-      <c r="M27" s="1"/>
+      <c r="M27" s="1">
+        <v>8.6</v>
+      </c>
       <c r="N27" s="1">
         <v>5</v>
       </c>
-      <c r="O27" s="1"/>
+      <c r="O27" s="1">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
@@ -2037,23 +2050,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -2103,13 +2116,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2138,9 +2151,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -3261,27 +3274,40 @@
       <c r="D64" s="1">
         <v>15</v>
       </c>
-      <c r="E64" s="1"/>
+      <c r="E64" s="1">
+        <f>32</f>
+        <v>32</v>
+      </c>
       <c r="F64" s="1">
         <v>10</v>
       </c>
-      <c r="G64" s="1"/>
+      <c r="G64" s="1">
+        <v>8.8000000000000007</v>
+      </c>
       <c r="H64" s="1">
         <v>7.4</v>
       </c>
-      <c r="I64" s="1"/>
+      <c r="I64" s="1">
+        <v>16.100000000000001</v>
+      </c>
       <c r="J64" s="1">
         <v>3</v>
       </c>
-      <c r="K64" s="1"/>
+      <c r="K64" s="1">
+        <v>4.5999999999999996</v>
+      </c>
       <c r="L64" s="1">
         <v>2.8</v>
       </c>
-      <c r="M64" s="1"/>
+      <c r="M64" s="1">
+        <v>3</v>
+      </c>
       <c r="N64" s="1">
         <v>3</v>
       </c>
-      <c r="O64" s="1"/>
+      <c r="O64" s="1">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
@@ -3572,23 +3598,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
-      <c r="N74" s="6"/>
-      <c r="O74" s="6"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3638,13 +3664,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3673,9 +3699,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -4797,27 +4823,40 @@
       <c r="D100" s="1">
         <v>22</v>
       </c>
-      <c r="E100" s="1"/>
+      <c r="E100" s="1">
+        <f>29.6</f>
+        <v>29.6</v>
+      </c>
       <c r="F100" s="1">
         <v>6</v>
       </c>
-      <c r="G100" s="1"/>
+      <c r="G100" s="1">
+        <v>9.1</v>
+      </c>
       <c r="H100" s="1">
         <v>4.5</v>
       </c>
-      <c r="I100" s="1"/>
+      <c r="I100" s="1">
+        <v>10.1</v>
+      </c>
       <c r="J100" s="1">
         <v>2</v>
       </c>
-      <c r="K100" s="1"/>
+      <c r="K100" s="1">
+        <v>5.4</v>
+      </c>
       <c r="L100" s="1">
         <v>2.7</v>
       </c>
-      <c r="M100" s="1"/>
+      <c r="M100" s="1">
+        <v>6.8</v>
+      </c>
       <c r="N100" s="1">
         <v>2</v>
       </c>
-      <c r="O100" s="1"/>
+      <c r="O100" s="1">
+        <v>6.3</v>
+      </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
@@ -5109,20 +5148,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -5139,6 +5164,20 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D36825-704C-401B-88EE-D21A216083E5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61164F6-78DF-482B-AD0C-3D01BF293A31}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1775,27 +1775,39 @@
       <c r="D28" s="1">
         <v>45</v>
       </c>
-      <c r="E28" s="1"/>
+      <c r="E28" s="1">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="F28" s="1">
         <v>35.1</v>
       </c>
-      <c r="G28" s="1"/>
+      <c r="G28" s="1">
+        <v>16.8</v>
+      </c>
       <c r="H28" s="1">
         <v>30</v>
       </c>
-      <c r="I28" s="1"/>
+      <c r="I28" s="1">
+        <v>4.5</v>
+      </c>
       <c r="J28" s="1">
         <v>6</v>
       </c>
-      <c r="K28" s="1"/>
+      <c r="K28" s="1">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="L28" s="1">
         <v>13.5</v>
       </c>
-      <c r="M28" s="1"/>
+      <c r="M28" s="1">
+        <v>4.8</v>
+      </c>
       <c r="N28" s="1">
         <v>5</v>
       </c>
-      <c r="O28" s="1"/>
+      <c r="O28" s="1">
+        <v>9.4</v>
+      </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
@@ -1811,27 +1823,39 @@
       <c r="D29" s="1">
         <v>45</v>
       </c>
-      <c r="E29" s="1"/>
+      <c r="E29" s="1">
+        <v>11.1</v>
+      </c>
       <c r="F29" s="1">
         <v>35.1</v>
       </c>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1">
+        <v>16.899999999999999</v>
+      </c>
       <c r="H29" s="1">
         <v>30</v>
       </c>
-      <c r="I29" s="1"/>
+      <c r="I29" s="1">
+        <v>16.100000000000001</v>
+      </c>
       <c r="J29" s="1">
         <v>6</v>
       </c>
-      <c r="K29" s="1"/>
+      <c r="K29" s="1">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="L29" s="1">
         <v>13.5</v>
       </c>
-      <c r="M29" s="1"/>
+      <c r="M29" s="1">
+        <v>4.5999999999999996</v>
+      </c>
       <c r="N29" s="1">
         <v>5</v>
       </c>
-      <c r="O29" s="1"/>
+      <c r="O29" s="1">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
@@ -1847,27 +1871,40 @@
       <c r="D30" s="1">
         <v>45</v>
       </c>
-      <c r="E30" s="1"/>
+      <c r="E30" s="1">
+        <f>11.1+68</f>
+        <v>79.099999999999994</v>
+      </c>
       <c r="F30" s="1">
         <v>35.1</v>
       </c>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1">
+        <v>16.899999999999999</v>
+      </c>
       <c r="H30" s="1">
         <v>30</v>
       </c>
-      <c r="I30" s="1"/>
+      <c r="I30" s="1">
+        <v>16.100000000000001</v>
+      </c>
       <c r="J30" s="1">
         <v>6</v>
       </c>
-      <c r="K30" s="1"/>
+      <c r="K30" s="1">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="L30" s="1">
         <v>13.5</v>
       </c>
-      <c r="M30" s="1"/>
+      <c r="M30" s="1">
+        <v>4.5999999999999996</v>
+      </c>
       <c r="N30" s="1">
         <v>5</v>
       </c>
-      <c r="O30" s="1"/>
+      <c r="O30" s="1">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -2050,23 +2087,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -2116,13 +2153,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2151,9 +2188,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -3323,27 +3360,40 @@
       <c r="D65" s="1">
         <v>15</v>
       </c>
-      <c r="E65" s="1"/>
+      <c r="E65" s="1">
+        <f>26.4</f>
+        <v>26.4</v>
+      </c>
       <c r="F65" s="1">
         <v>10</v>
       </c>
-      <c r="G65" s="1"/>
+      <c r="G65" s="1">
+        <v>5.9</v>
+      </c>
       <c r="H65" s="1">
         <v>7.4</v>
       </c>
-      <c r="I65" s="1"/>
+      <c r="I65" s="1">
+        <v>20.399999999999999</v>
+      </c>
       <c r="J65" s="1">
         <v>3</v>
       </c>
-      <c r="K65" s="1"/>
+      <c r="K65" s="1">
+        <v>3.8</v>
+      </c>
       <c r="L65" s="1">
         <v>2.8</v>
       </c>
-      <c r="M65" s="1"/>
+      <c r="M65" s="1">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="N65" s="1">
         <v>3</v>
       </c>
-      <c r="O65" s="1"/>
+      <c r="O65" s="1">
+        <v>7.3</v>
+      </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
@@ -3359,27 +3409,39 @@
       <c r="D66" s="1">
         <v>15</v>
       </c>
-      <c r="E66" s="1"/>
+      <c r="E66" s="1">
+        <v>27.4</v>
+      </c>
       <c r="F66" s="1">
         <v>10</v>
       </c>
-      <c r="G66" s="1"/>
+      <c r="G66" s="1">
+        <v>5.9</v>
+      </c>
       <c r="H66" s="1">
         <v>7.4</v>
       </c>
-      <c r="I66" s="1"/>
+      <c r="I66" s="1">
+        <v>19.3</v>
+      </c>
       <c r="J66" s="1">
         <v>3</v>
       </c>
-      <c r="K66" s="1"/>
+      <c r="K66" s="1">
+        <v>3.8</v>
+      </c>
       <c r="L66" s="1">
         <v>2.8</v>
       </c>
-      <c r="M66" s="1"/>
+      <c r="M66" s="1">
+        <v>2.5</v>
+      </c>
       <c r="N66" s="1">
         <v>3</v>
       </c>
-      <c r="O66" s="1"/>
+      <c r="O66" s="1">
+        <v>7.3</v>
+      </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
@@ -3395,27 +3457,40 @@
       <c r="D67" s="1">
         <v>15</v>
       </c>
-      <c r="E67" s="1"/>
+      <c r="E67" s="1">
+        <f>27.4+15</f>
+        <v>42.4</v>
+      </c>
       <c r="F67" s="1">
         <v>10</v>
       </c>
-      <c r="G67" s="1"/>
+      <c r="G67" s="1">
+        <v>5.9</v>
+      </c>
       <c r="H67" s="1">
         <v>7.4</v>
       </c>
-      <c r="I67" s="1"/>
+      <c r="I67" s="1">
+        <v>19.3</v>
+      </c>
       <c r="J67" s="1">
         <v>3</v>
       </c>
-      <c r="K67" s="1"/>
+      <c r="K67" s="1">
+        <v>3.8</v>
+      </c>
       <c r="L67" s="1">
         <v>2.8</v>
       </c>
-      <c r="M67" s="1"/>
+      <c r="M67" s="1">
+        <v>2.5</v>
+      </c>
       <c r="N67" s="1">
         <v>3</v>
       </c>
-      <c r="O67" s="1"/>
+      <c r="O67" s="1">
+        <v>7.3</v>
+      </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
@@ -3598,23 +3673,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3664,13 +3739,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3699,9 +3774,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -4872,27 +4947,39 @@
       <c r="D101" s="1">
         <v>22</v>
       </c>
-      <c r="E101" s="1"/>
+      <c r="E101" s="1">
+        <v>23.9</v>
+      </c>
       <c r="F101" s="1">
         <v>6</v>
       </c>
-      <c r="G101" s="1"/>
+      <c r="G101" s="1">
+        <v>11.2</v>
+      </c>
       <c r="H101" s="1">
         <v>4.5</v>
       </c>
-      <c r="I101" s="1"/>
+      <c r="I101" s="1">
+        <v>7.6</v>
+      </c>
       <c r="J101" s="1">
         <v>2</v>
       </c>
-      <c r="K101" s="1"/>
+      <c r="K101" s="1">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="L101" s="1">
         <v>2.7</v>
       </c>
-      <c r="M101" s="1"/>
+      <c r="M101" s="1">
+        <v>5.7</v>
+      </c>
       <c r="N101" s="1">
         <v>2</v>
       </c>
-      <c r="O101" s="1"/>
+      <c r="O101" s="1">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
@@ -4908,27 +4995,39 @@
       <c r="D102" s="1">
         <v>22</v>
       </c>
-      <c r="E102" s="1"/>
+      <c r="E102" s="1">
+        <v>24.3</v>
+      </c>
       <c r="F102" s="1">
         <v>6</v>
       </c>
-      <c r="G102" s="1"/>
+      <c r="G102" s="1">
+        <v>11.2</v>
+      </c>
       <c r="H102" s="1">
         <v>4.5</v>
       </c>
-      <c r="I102" s="1"/>
+      <c r="I102" s="1">
+        <v>7.6</v>
+      </c>
       <c r="J102" s="1">
         <v>2</v>
       </c>
-      <c r="K102" s="1"/>
+      <c r="K102" s="1">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="L102" s="1">
         <v>2.7</v>
       </c>
-      <c r="M102" s="1"/>
+      <c r="M102" s="1">
+        <v>5.5</v>
+      </c>
       <c r="N102" s="1">
         <v>2</v>
       </c>
-      <c r="O102" s="1"/>
+      <c r="O102" s="1">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
@@ -4944,27 +5043,40 @@
       <c r="D103" s="1">
         <v>22</v>
       </c>
-      <c r="E103" s="1"/>
+      <c r="E103" s="1">
+        <f>39.6</f>
+        <v>39.6</v>
+      </c>
       <c r="F103" s="1">
         <v>6</v>
       </c>
-      <c r="G103" s="1"/>
+      <c r="G103" s="1">
+        <v>11.2</v>
+      </c>
       <c r="H103" s="1">
         <v>4.5</v>
       </c>
-      <c r="I103" s="1"/>
+      <c r="I103" s="1">
+        <v>7.6</v>
+      </c>
       <c r="J103" s="1">
         <v>2</v>
       </c>
-      <c r="K103" s="1"/>
+      <c r="K103" s="1">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="L103" s="1">
         <v>2.7</v>
       </c>
-      <c r="M103" s="1"/>
+      <c r="M103" s="1">
+        <v>5.5</v>
+      </c>
       <c r="N103" s="1">
         <v>2</v>
       </c>
-      <c r="O103" s="1"/>
+      <c r="O103" s="1">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
@@ -5148,6 +5260,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -5164,20 +5290,6 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61164F6-78DF-482B-AD0C-3D01BF293A31}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F01F3DC-B789-4A02-996D-154C48DF0F7D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1920,27 +1920,40 @@
       <c r="D31" s="1">
         <v>45</v>
       </c>
-      <c r="E31" s="1"/>
+      <c r="E31" s="1">
+        <f>48.4+52</f>
+        <v>100.4</v>
+      </c>
       <c r="F31" s="1">
         <v>35.1</v>
       </c>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1">
+        <v>47.9</v>
+      </c>
       <c r="H31" s="1">
         <v>30</v>
       </c>
-      <c r="I31" s="1"/>
+      <c r="I31" s="1">
+        <v>37.700000000000003</v>
+      </c>
       <c r="J31" s="1">
         <v>6</v>
       </c>
-      <c r="K31" s="1"/>
+      <c r="K31" s="1">
+        <v>11.5</v>
+      </c>
       <c r="L31" s="1">
         <v>13.5</v>
       </c>
-      <c r="M31" s="1"/>
+      <c r="M31" s="1">
+        <v>12.7</v>
+      </c>
       <c r="N31" s="1">
         <v>5</v>
       </c>
-      <c r="O31" s="1"/>
+      <c r="O31" s="1">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
@@ -3506,27 +3519,40 @@
       <c r="D68" s="1">
         <v>15</v>
       </c>
-      <c r="E68" s="1"/>
+      <c r="E68" s="1">
+        <f>21.6+15</f>
+        <v>36.6</v>
+      </c>
       <c r="F68" s="1">
         <v>10</v>
       </c>
-      <c r="G68" s="1"/>
+      <c r="G68" s="1">
+        <v>20.399999999999999</v>
+      </c>
       <c r="H68" s="1">
         <v>7.4</v>
       </c>
-      <c r="I68" s="1"/>
+      <c r="I68" s="1">
+        <v>17.399999999999999</v>
+      </c>
       <c r="J68" s="1">
         <v>3</v>
       </c>
-      <c r="K68" s="1"/>
+      <c r="K68" s="1">
+        <v>8.9</v>
+      </c>
       <c r="L68" s="1">
         <v>2.8</v>
       </c>
-      <c r="M68" s="1"/>
+      <c r="M68" s="1">
+        <v>9.6</v>
+      </c>
       <c r="N68" s="1">
         <v>3</v>
       </c>
-      <c r="O68" s="1"/>
+      <c r="O68" s="1">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
@@ -5092,27 +5118,40 @@
       <c r="D104" s="1">
         <v>22</v>
       </c>
-      <c r="E104" s="1"/>
+      <c r="E104" s="1">
+        <f>31.6</f>
+        <v>31.6</v>
+      </c>
       <c r="F104" s="1">
         <v>6</v>
       </c>
-      <c r="G104" s="1"/>
+      <c r="G104" s="1">
+        <v>16.5</v>
+      </c>
       <c r="H104" s="1">
         <v>4.5</v>
       </c>
-      <c r="I104" s="1"/>
+      <c r="I104" s="1">
+        <v>5</v>
+      </c>
       <c r="J104" s="1">
         <v>2</v>
       </c>
-      <c r="K104" s="1"/>
+      <c r="K104" s="1">
+        <v>4.2</v>
+      </c>
       <c r="L104" s="1">
         <v>2.7</v>
       </c>
-      <c r="M104" s="1"/>
+      <c r="M104" s="1">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="N104" s="1">
         <v>2</v>
       </c>
-      <c r="O104" s="1"/>
+      <c r="O104" s="1">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F01F3DC-B789-4A02-996D-154C48DF0F7D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7664BC07-BDE0-4FF4-B9B8-AF5BB48EB734}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1969,27 +1969,39 @@
       <c r="D32" s="1">
         <v>45</v>
       </c>
-      <c r="E32" s="1"/>
+      <c r="E32" s="1">
+        <v>73.900000000000006</v>
+      </c>
       <c r="F32" s="1">
         <v>35.1</v>
       </c>
-      <c r="G32" s="1"/>
+      <c r="G32" s="1">
+        <v>53.7</v>
+      </c>
       <c r="H32" s="1">
         <v>30</v>
       </c>
-      <c r="I32" s="1"/>
+      <c r="I32" s="1">
+        <v>46.7</v>
+      </c>
       <c r="J32" s="1">
         <v>6</v>
       </c>
-      <c r="K32" s="1"/>
+      <c r="K32" s="1">
+        <v>17.2</v>
+      </c>
       <c r="L32" s="1">
         <v>13.5</v>
       </c>
-      <c r="M32" s="1"/>
+      <c r="M32" s="1">
+        <v>17.600000000000001</v>
+      </c>
       <c r="N32" s="1">
         <v>5</v>
       </c>
-      <c r="O32" s="1"/>
+      <c r="O32" s="1">
+        <v>9.8000000000000007</v>
+      </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
@@ -2100,23 +2112,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -2166,13 +2178,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2201,9 +2213,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -3568,27 +3580,40 @@
       <c r="D69" s="1">
         <v>15</v>
       </c>
-      <c r="E69" s="1"/>
+      <c r="E69" s="1">
+        <f>44.2</f>
+        <v>44.2</v>
+      </c>
       <c r="F69" s="1">
         <v>10</v>
       </c>
-      <c r="G69" s="1"/>
+      <c r="G69" s="1">
+        <v>17.399999999999999</v>
+      </c>
       <c r="H69" s="1">
         <v>7.4</v>
       </c>
-      <c r="I69" s="1"/>
+      <c r="I69" s="1">
+        <v>14.9</v>
+      </c>
       <c r="J69" s="1">
         <v>3</v>
       </c>
-      <c r="K69" s="1"/>
+      <c r="K69" s="1">
+        <v>8.3000000000000007</v>
+      </c>
       <c r="L69" s="1">
         <v>2.8</v>
       </c>
-      <c r="M69" s="1"/>
+      <c r="M69" s="1">
+        <v>8.6999999999999993</v>
+      </c>
       <c r="N69" s="1">
         <v>3</v>
       </c>
-      <c r="O69" s="1"/>
+      <c r="O69" s="1">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
@@ -3699,23 +3724,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
-      <c r="N74" s="6"/>
-      <c r="O74" s="6"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3765,13 +3790,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3800,9 +3825,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -5167,27 +5192,39 @@
       <c r="D105" s="1">
         <v>22</v>
       </c>
-      <c r="E105" s="1"/>
+      <c r="E105" s="1">
+        <v>40.4</v>
+      </c>
       <c r="F105" s="1">
         <v>6</v>
       </c>
-      <c r="G105" s="1"/>
+      <c r="G105" s="1">
+        <v>15.7</v>
+      </c>
       <c r="H105" s="1">
         <v>4.5</v>
       </c>
-      <c r="I105" s="1"/>
+      <c r="I105" s="1">
+        <v>14.8</v>
+      </c>
       <c r="J105" s="1">
         <v>2</v>
       </c>
-      <c r="K105" s="1"/>
+      <c r="K105" s="1">
+        <v>3.5</v>
+      </c>
       <c r="L105" s="1">
         <v>2.7</v>
       </c>
-      <c r="M105" s="1"/>
+      <c r="M105" s="1">
+        <v>4.2</v>
+      </c>
       <c r="N105" s="1">
         <v>2</v>
       </c>
-      <c r="O105" s="1"/>
+      <c r="O105" s="1">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
@@ -5299,20 +5336,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -5329,6 +5352,20 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7664BC07-BDE0-4FF4-B9B8-AF5BB48EB734}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756C512C-1BA8-4370-BF4A-7AAB7DCCCA71}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -2017,27 +2017,40 @@
       <c r="D33" s="1">
         <v>45</v>
       </c>
-      <c r="E33" s="1"/>
+      <c r="E33" s="1">
+        <f>48.6+30</f>
+        <v>78.599999999999994</v>
+      </c>
       <c r="F33" s="1">
         <v>35.1</v>
       </c>
-      <c r="G33" s="1"/>
+      <c r="G33" s="1">
+        <v>42.5</v>
+      </c>
       <c r="H33" s="1">
         <v>30</v>
       </c>
-      <c r="I33" s="1"/>
+      <c r="I33" s="1">
+        <v>39.299999999999997</v>
+      </c>
       <c r="J33" s="1">
         <v>6</v>
       </c>
-      <c r="K33" s="1"/>
+      <c r="K33" s="1">
+        <v>15.6</v>
+      </c>
       <c r="L33" s="1">
         <v>13.5</v>
       </c>
-      <c r="M33" s="1"/>
+      <c r="M33" s="1">
+        <v>12.5</v>
+      </c>
       <c r="N33" s="1">
         <v>5</v>
       </c>
-      <c r="O33" s="1"/>
+      <c r="O33" s="1">
+        <v>8.4</v>
+      </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
@@ -2112,23 +2125,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -2178,13 +2191,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2213,9 +2226,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -3629,27 +3642,40 @@
       <c r="D70" s="1">
         <v>15</v>
       </c>
-      <c r="E70" s="1"/>
+      <c r="E70" s="1">
+        <f>38.5</f>
+        <v>38.5</v>
+      </c>
       <c r="F70" s="1">
         <v>10</v>
       </c>
-      <c r="G70" s="1"/>
+      <c r="G70" s="1">
+        <v>15.4</v>
+      </c>
       <c r="H70" s="1">
         <v>7.4</v>
       </c>
-      <c r="I70" s="1"/>
+      <c r="I70" s="1">
+        <v>13.1</v>
+      </c>
       <c r="J70" s="1">
         <v>3</v>
       </c>
-      <c r="K70" s="1"/>
+      <c r="K70" s="1">
+        <v>7.8</v>
+      </c>
       <c r="L70" s="1">
         <v>2.8</v>
       </c>
-      <c r="M70" s="1"/>
+      <c r="M70" s="1">
+        <v>7.1</v>
+      </c>
       <c r="N70" s="1">
         <v>3</v>
       </c>
-      <c r="O70" s="1"/>
+      <c r="O70" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
@@ -3724,23 +3750,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3790,13 +3816,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3825,9 +3851,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -5240,27 +5266,40 @@
       <c r="D106" s="1">
         <v>22</v>
       </c>
-      <c r="E106" s="1"/>
+      <c r="E106" s="1">
+        <f>35.3</f>
+        <v>35.299999999999997</v>
+      </c>
       <c r="F106" s="1">
         <v>6</v>
       </c>
-      <c r="G106" s="1"/>
+      <c r="G106" s="1">
+        <v>11.9</v>
+      </c>
       <c r="H106" s="1">
         <v>4.5</v>
       </c>
-      <c r="I106" s="1"/>
+      <c r="I106" s="1">
+        <v>14.3</v>
+      </c>
       <c r="J106" s="1">
         <v>2</v>
       </c>
-      <c r="K106" s="1"/>
+      <c r="K106" s="1">
+        <v>3.1</v>
+      </c>
       <c r="L106" s="1">
         <v>2.7</v>
       </c>
-      <c r="M106" s="1"/>
+      <c r="M106" s="1">
+        <v>3.8</v>
+      </c>
       <c r="N106" s="1">
         <v>2</v>
       </c>
-      <c r="O106" s="1"/>
+      <c r="O106" s="1">
+        <v>2.2000000000000002</v>
+      </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
@@ -5336,6 +5375,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -5352,20 +5405,6 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(10,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756C512C-1BA8-4370-BF4A-7AAB7DCCCA71}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEC56CC-C1FB-4A34-9EFD-61E887443620}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,14 +205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,23 +504,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -570,13 +570,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -605,9 +605,9 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -2066,27 +2066,39 @@
       <c r="D34" s="1">
         <v>45</v>
       </c>
-      <c r="E34" s="1"/>
+      <c r="E34" s="1">
+        <v>57.5</v>
+      </c>
       <c r="F34" s="1">
         <v>35.1</v>
       </c>
-      <c r="G34" s="1"/>
+      <c r="G34" s="1">
+        <v>42.5</v>
+      </c>
       <c r="H34" s="1">
         <v>30</v>
       </c>
-      <c r="I34" s="1"/>
+      <c r="I34" s="1">
+        <v>60.4</v>
+      </c>
       <c r="J34" s="1">
         <v>6</v>
       </c>
-      <c r="K34" s="1"/>
+      <c r="K34" s="1">
+        <v>13.3</v>
+      </c>
       <c r="L34" s="1">
         <v>13.5</v>
       </c>
-      <c r="M34" s="1"/>
+      <c r="M34" s="1">
+        <v>14</v>
+      </c>
       <c r="N34" s="1">
         <v>5</v>
       </c>
-      <c r="O34" s="1"/>
+      <c r="O34" s="1">
+        <v>12.9</v>
+      </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
@@ -2125,23 +2137,23 @@
       <c r="O35" s="1"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -2191,13 +2203,13 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2226,9 +2238,9 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="1" t="s">
         <v>1</v>
       </c>
@@ -3691,27 +3703,40 @@
       <c r="D71" s="1">
         <v>15</v>
       </c>
-      <c r="E71" s="1"/>
+      <c r="E71" s="1">
+        <f>32.8</f>
+        <v>32.799999999999997</v>
+      </c>
       <c r="F71" s="1">
         <v>10</v>
       </c>
-      <c r="G71" s="1"/>
+      <c r="G71" s="1">
+        <v>14</v>
+      </c>
       <c r="H71" s="1">
         <v>7.4</v>
       </c>
-      <c r="I71" s="1"/>
+      <c r="I71" s="1">
+        <v>23.1</v>
+      </c>
       <c r="J71" s="1">
         <v>3</v>
       </c>
-      <c r="K71" s="1"/>
+      <c r="K71" s="1">
+        <v>6.1</v>
+      </c>
       <c r="L71" s="1">
         <v>2.8</v>
       </c>
-      <c r="M71" s="1"/>
+      <c r="M71" s="1">
+        <v>6.2</v>
+      </c>
       <c r="N71" s="1">
         <v>3</v>
       </c>
-      <c r="O71" s="1"/>
+      <c r="O71" s="1">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
@@ -3750,23 +3775,23 @@
       <c r="O72" s="1"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
-      <c r="N74" s="6"/>
-      <c r="O74" s="6"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
@@ -3816,13 +3841,13 @@
       </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3851,9 +3876,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="1" t="s">
         <v>1</v>
       </c>
@@ -5315,27 +5340,39 @@
       <c r="D107" s="1">
         <v>22</v>
       </c>
-      <c r="E107" s="1"/>
+      <c r="E107" s="1">
+        <v>28.1</v>
+      </c>
       <c r="F107" s="1">
         <v>6</v>
       </c>
-      <c r="G107" s="1"/>
+      <c r="G107" s="1">
+        <v>15.1</v>
+      </c>
       <c r="H107" s="1">
         <v>4.5</v>
       </c>
-      <c r="I107" s="1"/>
+      <c r="I107" s="1">
+        <v>12.5</v>
+      </c>
       <c r="J107" s="1">
         <v>2</v>
       </c>
-      <c r="K107" s="1"/>
+      <c r="K107" s="1">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="L107" s="1">
         <v>2.7</v>
       </c>
-      <c r="M107" s="1"/>
+      <c r="M107" s="1">
+        <v>8.6</v>
+      </c>
       <c r="N107" s="1">
         <v>2</v>
       </c>
-      <c r="O107" s="1"/>
+      <c r="O107" s="1">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
@@ -5375,20 +5412,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="N40:O40"/>
@@ -5405,6 +5428,20 @@
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
